--- a/data/output/procurement_qa_dataset.xlsx
+++ b/data/output/procurement_qa_dataset.xlsx
@@ -493,22 +493,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cand_002</t>
+          <t>cand_001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>What does TTR stand for and what does it measure in the context of supply chain disruptions?</t>
+          <t>What are some options to manage supply chain risks?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>TTR stands for Time To Recovery, which measures the time it takes a company to restore full operational output following a major supply chain disruption.</t>
+          <t>Some options to manage supply chain risks include addressing sourcing risks as an integral part of the product design and engineering, managing stock levels, considering alternative sourcing and flexible logistical arrangements, using general purpose contingency arrangements such as business interruption insurance and proactive business relationship management, supplier questionnaires, risk assessments, audits, and certification, awareness campaigns and training programs, using business intelligence from big data analytics and continuous monitoring, optimizing redundancy, and implementing comprehensive digitalization and modernization of management methods.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>12 TTR measures the time it takes a company to restore full operational output following a major supply chain disruption. The determination of TTR assumes that a facility is essentially unusable due to a major event, requiring extensive repairs and reconstruction, as well as re-sourcing and re-qualifying of key equipment used in manufacturing and other operations. In essence, Time To Recovery is a measure of how long it would take a supply chain to return to normal after suffering</t>
+          <t>25 Supply chain resilience options edit Some options to engineer an acceptable risk level in supply chains include: Addressing sourcing risks as an integral part of the product design and engineering (e.g. preferring standardized multi-sourced commodities over custom or unique supplies from sole suppliers) Managing stock levels both statically and dynamically Considering alternative sourcing and flexible logistical arrangements (e.g. trucks to supplement or replace trains) General purpose contingency arrangements such as business interruption insurance and proactive business relationship management (building mutual understanding and trust) Supplier questionnaires, risk assessments, audits and certification, both for initial supplier selection and subsequently (e.g. refreshed prior to major changes such as new products, or in response to issues arising) Awareness campaigns and training programs The use of business intelligence from big data analytics and continuous monitoring for predictive security measures vs. clean up Redundancy optimization (e.g. focusing redundancy efforts on business- or mission-critical products) Slick incident management where time is of the essence Postponement, product substitution and other forms of downstream supply chain management (assisting customers) Comprehensive digitalization and modernization of management methods</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -518,11 +518,11 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>logistics and KPIs</t>
+          <t>risk and sustainability</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.944</v>
+        <v>0.953</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1</v>
@@ -531,36 +531,36 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cand_004</t>
+          <t>cand_002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Why do Pekša and Grabis suggest decoupling decision-making logic from ERP systems in their research?</t>
+          <t>What does TTR measure in the context of supply chain management?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Pekša and Grabis suggest decoupling decision-making logic from ERP systems because decision-making techniques should be modifiable, scalable, and portable. This decoupling enables the usage of advanced decision-making techniques, whereas implementing decision-making directly into existing ERP systems is seen as inflexible and cost-intensive, leading to competitive disadvantages.</t>
+          <t>TTR measures the time it takes a company to restore full operational output following a major supply chain disruption.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>tologies and propose an integration framework based on ontology learning including a basic workﬂow (Ma and Moln´ar, 2019). Pekˇsa and Grabis (Pekˇsa and Gra- bis, 2018) reviewed existing research on the decision- making capabilities of ERP systems. They identiﬁed different approaches for integrating decision-making logic for companies. Since decision-making tech- niques should be modiﬁable, scalable, and portable, they suggest decoupling decision-making logic from ERP systems. This decoupling enables the usage of advanced decision-making techniques. Implementing decision-making directly into existing ERP systems is seen as inﬂexible and cost-intensive, leading to com- petitive disadvantages. In the last years, many articles regarding SCM and procurement are published. For example, Re- jeb et al. (Rejeb et al., 2018) outline the potential of new technologies like Big Data analysis, Automatiza- tion and Robotics, IoT, and Blockchain Technology in procurement-related work since the entire supply chain has already and will continue to have techno- logical shifts. Nevertheless, the article does not fo- cus on ERP systems. However, Tarigan et al. (Tarigan</t>
+          <t>12 TTR measures the time it takes a company to restore full operational output following a major supply chain disruption. The determination of TTR assumes that a facility is essentially unusable due to a major event, requiring extensive repairs and reconstruction, as well as re-sourcing and re-qualifying of key equipment used in manufacturing and other operations. In essence, Time To Recovery is a measure of how long it would take a supply chain to return to normal after suffering</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://arxiv.org/pdf/2303.03882</t>
+          <t>https://en.wikipedia.org/wiki/Supply_chain_risk_management</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>e-procurement and data standards</t>
+          <t>logistics and KPIs</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.903</v>
+        <v>0.953</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>1</v>
@@ -569,36 +569,36 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>cand_005</t>
+          <t>cand_006</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>What method does the passage suggest for assessing the effectiveness of public procurement plans?</t>
+          <t>What are monetarily quantifiable criteria in procurement evaluation?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>The passage suggests conducting interviews with procurers to assess the degree of training and knowledge, as well as recognizing and understanding the obstacles in the implementation of SPP in their respective administration.</t>
+          <t>Monetarily quantifiable criteria in procurement evaluation are factors that can be measured in monetary terms and are specified in the Procurement Documents to determine the evaluated financial cost of each Bid/Proposal. Examples include margin of domestic preference, time schedule adjustment, payment schedule adjustment, life-cycle costing, functional guarantees min/max adjustment, and adjustments for nonmaterial non-conformities.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11 Project set up and governance structure establishment In the project organization and set up in pilot country of Mauritius, the NFO (Mauritius public procurement office) set up monthly and biweekly newsletters on the purpose of public procurement which was then used as a communication device for later projects, activities, and events, along with other relevant information 21 Assessment, review, and prioritization Recommended method of assessing the effectiveness of public procurement plans is conducting interviews with procurers as to assess the degree of training and knowledge. Recognize and understand the obstacles in the implementation of SPP in their respective administration as well as identifying products and services which are considered a priority for the well-functioning of such projects and policies.</t>
+          <t>There are two main types of evaluation and qualification criteria. a. Monetarily quantifiable criteria When setting monetarily quantifiable Evaluation Criteria, the Procurement Documents shall specify the relevant factors to be considered in the Bid/Proposal evaluation and the manner in A BEGINNER’S GUIDE FOR BORROWERS: PROCUREMENT UNDER WORLD BANK INVESTMENT PROJECT FINANCING 24 which they will be applied for the purpose of determining the evaluated financial cost of each Bid/Proposal. Examples of where monetarily quantifiable criteria may be applied to determine the total eval- uated Bid/Proposal financial cost may include, among others: i. margin of domestic preference (if agreed with the Bank) ii.  time schedule adjustment iii.  payment schedule adjustment iv.  life-cycle costing v.  functional guarantees min/max adjustment vi.  adjustments for nonmaterial non-conformities</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sustainable_procurement</t>
+          <t>https://thedocs.worldbank.org/en/doc/caf6a3f677305292d799dbe55fd83bfe-0290012023/original/PROCUREMENT-Beginners-Guide-to-IPF-WEB-VERSION-Nov-2023.pdf</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>procurement policy and compliance</t>
+          <t>tender process</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.834</v>
+        <v>0.822</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1</v>
@@ -607,36 +607,36 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>cand_006</t>
+          <t>cand_007</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>What are some examples of monetarily quantifiable criteria that can be used to determine the total evaluated Bid/Proposal financial cost?</t>
+          <t>What does the term 'indictment' mean in the context of procurement regulations?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Examples of monetarily quantifiable criteria include the margin of domestic preference, time schedule adjustment, payment schedule adjustment, life-cycle costing, functional guarantees min/max adjustment, and adjustments for nonmaterial non-conformities.</t>
+          <t>The term 'indictment' means indictment for a criminal offense. An information or other filing by competent authority charging a criminal offense is given the same effect as an indictment.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>There are two main types of evaluation and qualification criteria. a. Monetarily quantifiable criteria When setting monetarily quantifiable Evaluation Criteria, the Procurement Documents shall specify the relevant factors to be considered in the Bid/Proposal evaluation and the manner in A BEGINNER’S GUIDE FOR BORROWERS: PROCUREMENT UNDER WORLD BANK INVESTMENT PROJECT FINANCING 24 which they will be applied for the purpose of determining the evaluated financial cost of each Bid/Proposal. Examples of where monetarily quantifiable criteria may be applied to determine the total eval- uated Bid/Proposal financial cost may include, among others: i. margin of domestic preference (if agreed with the Bank) ii.  time schedule adjustment iii.  payment schedule adjustment iv.  life-cycle costing v.  functional guarantees min/max adjustment vi.  adjustments for nonmaterial non-conformities</t>
+          <t>(2) Conducts business, or reasonably may be expected to conduct business, with the Government as an agent or representative of another contractor Indictment means indictment for a criminal offense. An information or other filing by competent authority charging a criminal offense is given the same effect as an indictment Legal proceedings means any civil judicial proceeding to which the Government is a party or any criminal proceeding. The term includes appeals from such proceedings. Nonprocurement Common Rule means the procedures used by Federal Executive Agencies to suspend, debar, or exclude individuals or entities from participation in nonprocurement transactions under Executive Order 12549. Examples of nonprocurement transactions are grants, cooperative agreements, scholarships, fellowships, contracts of assistance, loans, loan guarantees, subsidies, insurance , payments for specified use, and donation agreements. See 2 CFR part 180 and agency enacting regulations in 2 CFR subtitle B Pre-notice letter means a written correspondence issued to a contractor in a suspension or debarment matter, which does not immediately result in an exclusion or ineligibility. The letter is issued at the discretion of the suspending and debarring official</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://thedocs.worldbank.org/en/doc/caf6a3f677305292d799dbe55fd83bfe-0290012023/original/PROCUREMENT-Beginners-Guide-to-IPF-WEB-VERSION-Nov-2023.pdf</t>
+          <t>https://www.acquisition.gov/far/part-9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>tender process</t>
+          <t>contract management</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.619</v>
+        <v>0.844</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>What should sustainable procurement requirements be based on according to the passage?</t>
+          <t>What should sustainable procurement requirements be based on?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -683,36 +683,36 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>cand_011</t>
+          <t>cand_010</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>What are some benefits of following OCDS rules and guidance when publishing contracting data?</t>
+          <t>What is the purpose of incorporating supply chain considerations in the works requirements/specification?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Following OCDS rules and guidance will help you and your users to access clear definitions for the meaning, structure, and format of your data, access a growing ecosystem of reusable tools and methodologies for working with OCDS data, compare your data with other publishers' data to examine value for money and other types of analysis, and check the structure, format, and quality of your data against the OCDS schema.</t>
+          <t>Incorporating supply chain considerations in the works requirements/specification can be a critical element that influences the success of the relationship between the parties and how future supply chain challenges are managed. Borrowers should consider the Project Development Objectives and the VfM principles when drafting the works requirements/specification (and the final contract), and design them with a “fit for purpose” mindset, that is to say, one that is proportionate to the complexity, risk, and value of the procurement.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>While JSON is the default format, a good publication will publish tabular formats as well both so that more usersâ needs can be satisfied. No matter what type of contracting data you are working with or format you publish in, following OCDS rules and guidance will help you and your users to: Access clear definitions for the meaning, structure and format of your data Access a growing ecosystem of reusable tools and methodologies for working with OCDS data Compare your data with other publishersâ data to examine value for money and other types of analysis Check the structure, format and quality of your data against the OCDS schema Note To learn more, go to the next page in the Primer: How is OCDS data published? You can also review the further resources below to go deeper into the subjects introduced on this page. Guidance to implementing OCDS Video Learning Guide to the OCDS OCP Learning: Publishing OCDS Data Open Contracting Playbook: Component 2</t>
+          <t>Is the evidence required proportionate to the risks? ☐ Yes ☐ No Can the terms and conditions of the contract address these risks? ☐ Yes ☐ No Do the terms and conditions pass unnecessary risks to the Supplier/Contractor? ☐ Yes ☐ No Including Supply Chain Considerations in the Works Requirements/Specification The Bank’s SPDs include general provisions related to SCM. While the Bank does not allow a Borrower to adjust standard contract terms in SPDs, additional supply chain considerations can be addressed in the Works requirements/specification. Including such SCM considerations can be a critical element that influences the success of the relationship between the parties and how future SCM challenges are managed. Borrowers should therefore consider the Project Development Objectives and the VfM principles when drafting the Works requirements/specification (and the final contract), and design them with a “fit for purpose” mindset, that is to say, one that is proportionate to the complexity, risk, and value of the procurement. Where appropriate, Borrowers should include in the Works requirements/specification additional SCM expectations for Suppliers/Contractors, which can spell out further SCM requirements that</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://standard.open-contracting.org/latest/en/getting_started/building_blocks/</t>
+          <t>https://thedocs.worldbank.org/en/doc/1c3b517f003b53a2e2e170e93124be84-0290032023/original/World-Bank-Supply-Chain-Management-Guidance.pdf</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>e-procurement and data standards</t>
+          <t>supplier evaluation</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.92</v>
+        <v>0.929</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1</v>
@@ -721,36 +721,36 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>cand_012</t>
+          <t>cand_011</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>What types of national legislation might impact supply chain management in a project?</t>
+          <t>What benefits does following OCDS rules and guidance provide to data publishers and users?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>National legislation might impact supply chain management by requiring environmental and social risk assessments, specifying land use processes, setting obligations related to biodiversity, and imposing specific requirements for stakeholder engagement and emission levels. For example, national legislation may require carrying out environmental and social risk assessments for proposed projects.</t>
+          <t>Following OCDS rules and guidance helps data publishers and users to access clear definitions for the meaning, structure, and format of their data, access a growing ecosystem of reusable tools and methodologies for working with OCDS data, compare their data with other publishers' data to examine value for money and other types of analysis, and check the structure, format, and quality of their data against the OCDS schema.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>hensive labor legislation, covering terms and conditions of work, occupational health and safety, and protection for vulnerable groups. National legislation may include requirements to carry out environ- mental and social risk assessments for proposed projects; specify processes for use of land or land acquisition; set out obligations relating to biodiversity; or have specific requirements for engagement and consultation with different stakeholders. There can also be specific requirements for maximum emission levels, quality of water discharge, and noise levels. In addition to national legislation, there may also be regional and local legislation that needs to be adhered to. Governments may also be subject to different international agreements or conventions, which apply when a government is a party or has ratified these, that are relevant to SCM for the proposed project. Examples41 include the ILO Labor Standards, the Paris Agreement, the Aarhus Convention, the Convention on Biological Diversity, the Convention on Migratory Species, and the World Heritage Convention. ANNEX SUPPL Y CHAIN MANAGEMENT: AN INTRODUCTION AND PRACTICAL TOOLSET FOR PROCUREMENT PRACTITIONERS</t>
+          <t>While JSON is the default format, a good publication will publish tabular formats as well both so that more usersâ needs can be satisfied. No matter what type of contracting data you are working with or format you publish in, following OCDS rules and guidance will help you and your users to: Access clear definitions for the meaning, structure and format of your data Access a growing ecosystem of reusable tools and methodologies for working with OCDS data Compare your data with other publishersâ data to examine value for money and other types of analysis Check the structure, format and quality of your data against the OCDS schema Note To learn more, go to the next page in the Primer: How is OCDS data published? You can also review the further resources below to go deeper into the subjects introduced on this page. Guidance to implementing OCDS Video Learning Guide to the OCDS OCP Learning: Publishing OCDS Data Open Contracting Playbook: Component 2</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://thedocs.worldbank.org/en/doc/1c3b517f003b53a2e2e170e93124be84-0290032023/original/World-Bank-Supply-Chain-Management-Guidance.pdf</t>
+          <t>https://standard.open-contracting.org/latest/en/getting_started/building_blocks/</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>procurement policy and compliance</t>
+          <t>e-procurement and data standards</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.899</v>
+        <v>0.63</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1</v>
@@ -759,36 +759,36 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>cand_014</t>
+          <t>cand_012</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Under what circumstances can a debarment be extended for an additional period of one year?</t>
+          <t>What does national legislation typically cover in the context of supply chain management?</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>A debarment can be extended for an additional period of one year if the Secretary of Homeland Security or the Attorney General determines that the contractor continues to be in violation of the employment provisions of the Immigration and Nationality Act.</t>
+          <t>National legislation typically covers terms and conditions of work, occupational health and safety, and protection for vulnerable groups. It may also include requirements for environmental and social risk assessments, processes for land use or acquisition, obligations related to biodiversity, and specific requirements for stakeholder engagement and consultation.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>not be extended solely on the basis of the facts and circumstances upon which the initial debarment action was based. Debarments under 9.406-2 (b)(2) may be extended for additional periods of one year if the Secretary of Homeland Security or the Attorney General determines that the contractor continues to be in violation of the employment provisions of the Immigration and Nationality Act. If debarment for an additional period is determined to be necessary, the procedures of</t>
+          <t>hensive labor legislation, covering terms and conditions of work, occupational health and safety, and protection for vulnerable groups. National legislation may include requirements to carry out environ- mental and social risk assessments for proposed projects; specify processes for use of land or land acquisition; set out obligations relating to biodiversity; or have specific requirements for engagement and consultation with different stakeholders. There can also be specific requirements for maximum emission levels, quality of water discharge, and noise levels. In addition to national legislation, there may also be regional and local legislation that needs to be adhered to. Governments may also be subject to different international agreements or conventions, which apply when a government is a party or has ratified these, that are relevant to SCM for the proposed project. Examples41 include the ILO Labor Standards, the Paris Agreement, the Aarhus Convention, the Convention on Biological Diversity, the Convention on Migratory Species, and the World Heritage Convention. ANNEX SUPPL Y CHAIN MANAGEMENT: AN INTRODUCTION AND PRACTICAL TOOLSET FOR PROCUREMENT PRACTITIONERS</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.acquisition.gov/far/part-9</t>
+          <t>https://thedocs.worldbank.org/en/doc/1c3b517f003b53a2e2e170e93124be84-0290032023/original/World-Bank-Supply-Chain-Management-Guidance.pdf</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>contract management</t>
+          <t>procurement policy and compliance</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.98</v>
+        <v>0.907</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1</v>
@@ -797,22 +797,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>cand_017</t>
+          <t>cand_013</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>What does SCM stand for and what does it refer to?</t>
+          <t>What is the purpose of a procurement approach in the context of project development?</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>SCM stands for Supply Chain Management, which refers to the coordination of activities needed to provide a final product or service. These activities start with the raw materials and end with the delivery of the final product or service to the end customer. At the end of the product or asset’s usable life, supply chains are also responsible for coordinating the recycling, remanufacturing, or disposal of the final product.</t>
+          <t>The purpose of a procurement approach is to award contracts that deliver the Project Development Objectives and Value for Money. This includes the procurement arrangements, procurement risk management, contract strategy, market engagement, requirements drafting, and contract management (where appropriate).</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Develop strategy Assess the market and operating environment and determine procurement approach (PPSD). Invite oﬀers Request oﬀers from the market e.g. RFS or RFP. Answer questions from the market. Evaluate oﬀers Compare oﬀers and determine most advantageous bid/proposal. Manage contract Finalize Contract Management Plan and implement monitoring, evaluation and payment systems. Ensure both parties meet their obligations. 02 04 06 01 03 05 07 FIGURE I The Bank’s procurement process What is Supply Chain Management? SCM refers to the coordination of activities needed to provide a final product or service. These activ- ities start with the raw materials and end with the delivery of the final product or service to the end customer. At the end of the product or asset’s usable life, supply chains are also responsible for coor- dinating the recycling, remanufacturing (i.e., the rebuilding of a product to its original specifications SECTION I: INTRODUCTION using reused parts), or disposal of the final product. The supply chain captures all Organizations and activities that are responsible for or can influence this process, including Suppliers/Contractors, logistics Organizations, and governmental agencies (e.g., customs). Understanding and managing the supply chain is important for Borrowers procuring goods from Manu-</t>
+          <t>development objectives of the project and deliver VfM. iii COMMON ABBREVIATIONS AND DEFINED TERMS Abbreviation/term Full terminology/definition Prequalification The shortlisting process which can be used prior to inviting Request for Bids in the procurement of Goods, Works or Non-consulting Services. Procurement Approach Procurement approach is the overall design of “fit for purpose” procurement to award contracts that deliver the Project Development Objectives and Value for Money. This includes the procurement arrangements, procurement risk management, contract strategy, market engagement, requirements drafting and contract management (where appropriate). Project Development Objectives Project Development Objectives (PDOs) are set out in the approved Project Concept Note and are considered mandatory unless analysis demonstrates the need for adjustment. Procurement Documents A generic term used to cover all Procurement Documents issued by the Borrower soliciting applications/Bids/Proposals. Procurement Documents include prequalification document, initial selection document, Request for Bids document, Request for Proposal document, forms of contracts, and</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -822,11 +822,11 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>supplier evaluation</t>
+          <t>tender process</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.606</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1</v>
@@ -835,36 +835,36 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>cand_022</t>
+          <t>cand_018</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>What is the title of the book mentioned in the passage about supply chain management?</t>
+          <t>What is the Open Contracting Data Standard (OCDS)?</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>The title of the book mentioned in the passage is 'Supply-Chain-Management in stürmischen Zeiten'.</t>
+          <t>The Open Contracting Data Standard (OCDS) is a free, non-proprietary open data standard for public contracting, implemented by over 30 governments around the world. It describes how to publish data and documents about contracting processes for goods, works and services.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11 Collaboration 26 See also edit Supply chain security Cybersecurity Volume risk References edit cf. Andreas Wieland, Carl Marcus Wallenburg (2011): Supply-Chain-Management in stürmischen Zeiten . Berlin. Heckmann, Iris; Comes, Tina; Nickel, Stefan (2015). "A Critical Review on Supply Chain Risk – Definition, Measure and Modeling" Omega 52 (April 2015): 119– 132. doi 10.1108/09600031211281411 hdl 10398/9016 Brindley, Clare (2004). Supply Chain Risk . England: Ashgate Publishing Ltd. p. 80. ISBN 0-7546-3902-9 McKinsey, Understanding supply chain risk: A McKinsey Global Survey</t>
+          <t>Docs Primer What is the OCDS and why use it? View page source What is the OCDS and why use it? Â¶ Objectives This page will: Introduce the Open Contracting Data Standard (OCDS) Show the key concepts behind the OCDS Describe the relationship between the OCDS and open contracting The Open Contracting Data Standard (OCDS) is a free, non-proprietary open data standard for public contracting, implemented by over 30 governments around the world. It describes how to publish data and documents about contracting processes for goods, works and services. There are three concepts behind the Open Contracting Data Standard: Open Contracting is about publishing and using open, accessible and timely information on public contracting to engage citizens and businesses to fix problems and deliver results. These results include improving the efficiency, effectiveness and integrity of a public contracting system. Open Data is data that can be freely used, modified, and shared by anyone for any purpose. This requires data to be accessible and machine-readable, and for permission to be granted for reuse. Data Standard defines the structure and meaning of data in order to resolve ambiguity and help systems and people interpret it.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Supply_chain_risk_management</t>
+          <t>https://standard.open-contracting.org/latest/en/primer/what/</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>risk and sustainability</t>
+          <t>e-procurement and data standards</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.973</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1</v>
@@ -873,36 +873,36 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>cand_023</t>
+          <t>cand_021</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>What are the responsibilities of the seller and buyer under an FOB contract according to Incoterms 1980?</t>
+          <t>What conditions must be met for a contract to be considered nonresponsible under the given criteria?</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Under an FOB contract, the seller is responsible for delivering the goods on board a vessel designated by the buyer, and arranging for export clearance. The buyer is responsible for the cost of marine freight transportation, bill of lading fees, insurance, unloading, and transportation costs from the arrival port to the destination. However, FOB should only be used for non-containerized seafreight and inland waterway transport, and its use for all modes of transport can introduce contractual risks.</t>
+          <t>A contract is considered nonresponsible if it is valued at more than the simplified acquisition threshold, the determination of nonresponsibility is based on a lack of satisfactory performance record or a satisfactory record of integrity and business ethics, and the Small Business Administration does not issue a Certificate of Competency.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21 Therefore, FOB contract requires a seller to deliver goods on board a vessel that is to be designated by the buyer in a manner customary at the particular port. In this case, the seller must also arrange for export clearance. On the other hand, the buyer pays cost of marine freight transportation, bill of lading fees, insurance, unloading and transportation cost from the arrival port to destination. Since Incoterms 1980 introduced the Incoterm FCA, FOB should only be used for non-containerized seafreight and inland waterway transport. However, FOB is commonly used incorrectly for all modes of transport despite the contractual risks that this can introduce. In some common law countries such as the United States of America</t>
+          <t>) if- (A) The contract is valued at more than the simplified acquisition threshold (B) The determination of nonresponsibility is based on lack of satisfactory performance record or satisfactory record of integrity and business ethics; and (C) The Small Business Administration does not issue a Certificate of Competency. (ii) The contracting officer is responsible for the timely submission, within 3 working days, and sufficiency, and accuracy of the documentation regarding the nonresponsibility determination. (iii) As required by section 3010 of the Supplemental Appropriations Act, 2010 (Pub. L. 111-212), all information posted in FAPIIS on or after April 15, 2011, except past performance reviews, will be publicly available.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Incoterms</t>
+          <t>https://www.acquisition.gov/far/part-9</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>logistics and KPIs</t>
+          <t>contract management</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.944</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1</v>
@@ -911,36 +911,36 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>cand_025</t>
+          <t>cand_022</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>What is the ultimate goal of the OCDS according to the passage?</t>
+          <t>What is the purpose of reviewing supply chain risk in procurement?</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>The ultimate goal of the OCDS is to help deliver open contracting using standardized open data.</t>
+          <t>The purpose of reviewing supply chain risk in procurement is to identify and manage potential risks that could impact the supply chain, ensuring the stability and security of the supply chain.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>The OCDS builds on all three of these concepts, and the ultimate goal of the OCDS is to help deliver open contracting using standardized open data. The OCDS describes how to publish data and documents for the procurement of goods, works, and services. It makes contracting data available for anyone to use, modify, and share, for any purpose. The OCDS can be adapted to meet your needs. Whether purchasing medicines, running a municipal recycling program or building an airport, the OCDS helps you organize and publish all relevant data and documents during the process. The OCDS is not an electronic procurement system or database. But it can inform how data is collected, stored and published in these systems. The OCDS can help make sure that the contracting data you collect and publish meet global best practices and are fit-for-purpose to meet the needs of a range of different users. The OCDS helps to increase transparency, enables deeper analysis of contracting data, and facilitates the use of data by a wide range of stakeholders.</t>
+          <t>11 Collaboration 26 See also edit Supply chain security Cybersecurity Volume risk References edit cf. Andreas Wieland, Carl Marcus Wallenburg (2011): Supply-Chain-Management in stürmischen Zeiten . Berlin. Heckmann, Iris; Comes, Tina; Nickel, Stefan (2015). "A Critical Review on Supply Chain Risk – Definition, Measure and Modeling" Omega 52 (April 2015): 119– 132. doi 10.1108/09600031211281411 hdl 10398/9016 Brindley, Clare (2004). Supply Chain Risk . England: Ashgate Publishing Ltd. p. 80. ISBN 0-7546-3902-9 McKinsey, Understanding supply chain risk: A McKinsey Global Survey</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://standard.open-contracting.org/latest/en/primer/what/</t>
+          <t>https://en.wikipedia.org/wiki/Supply_chain_risk_management</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>e-procurement and data standards</t>
+          <t>risk and sustainability</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.93</v>
+        <v>0.916</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>1</v>
@@ -949,22 +949,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>cand_026</t>
+          <t>cand_023</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>What is the name of the United Nations code used for trade and transport locations mentioned in the passage?</t>
+          <t>What does FOB stand for in procurement and supply chain contracts?</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>The United Nations Code for Trade and Transport Locations (UN/LOCODE) is mentioned in the passage.</t>
+          <t>FOB stands for Free On Board in procurement and supply chain contracts.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine United Nations Code for Trade and Transport Locations (UN/LOCODE) International trade Terminology Absolute advantage Balance of payments Balance of trade Capital account Comparative advantage Current account Export-oriented industrialization Fair trade Foreign exchange reserves Globalization Global labor arbitrage Import substitution industrialization Multinational corporation Net capital outflow Outsourcing Tariff Trade justice Trade war Trading nation Organizations and policies International Monetary Fund UN Trade and Development World Bank Group World Trade Organization International Trade Centre International Chamber of Commerce Bilateral investment treaty Economic integration Incoterms ATA Carnet Free-trade zone Special economic zone Trade agreement Trade barrier Trade bloc Political economy Free trade Adam Smith The Wealth of Nations Corn Laws Mercantilism Protectionism Economic nationalism Autarky Dedollarisation Withdrawal from the eurozone Regional organizations Americas Andean Community Caribbean Community Central American Integration System Mercosur Asia-Pacific Association of Southeast Asian Nations Regional Comprehensive Economic Partnership South Asian Association for Regional Cooperation Europe, Central Asia, and North Asia Customs Union of the Eurasian Economic Union Eurasian Economic Union European Union Customs Union Middle East and North Africa Arab Customs Union Gulf Cooperation Council Subsaharan Africa East African Community Economic and Monetary Community of Central Africa Southern African Customs Union West African Economic and Monetary Union Exports by product</t>
+          <t>21 Therefore, FOB contract requires a seller to deliver goods on board a vessel that is to be designated by the buyer in a manner customary at the particular port. In this case, the seller must also arrange for export clearance. On the other hand, the buyer pays cost of marine freight transportation, bill of lading fees, insurance, unloading and transportation cost from the arrival port to destination. Since Incoterms 1980 introduced the Incoterm FCA, FOB should only be used for non-containerized seafreight and inland waterway transport. However, FOB is commonly used incorrectly for all modes of transport despite the contractual risks that this can introduce. In some common law countries such as the United States of America</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -974,11 +974,11 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>procurement policy and compliance</t>
+          <t>logistics and KPIs</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.836</v>
+        <v>0.878</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>1</v>
@@ -987,36 +987,36 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>cand_027</t>
+          <t>cand_025</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>What are the two types of financing provided by the Bank under Investment Project Financing (IPF)?</t>
+          <t>What is the purpose of the OCDS?</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>The two types of financing provided by the Bank under Investment Project Financing (IPF) are an IBRD loan or an IDA credit/grant or guarantee.</t>
+          <t>The OCDS helps to increase transparency, enables deeper analysis of contracting data, and facilitates the use of data by a wide range of stakeholders.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>FIGURE 1 The five World Bank Group Institutions SECTION I: INTRODUCTION Investment Project Financing Investment Project Financing (IPF) is one of the ways in which Bank financing is provided to countries. This financing may take the form of an IBRD loan or IDA credit/grant or guarantee. IPF supports projects with defined development objectives, activities, and results, and disburses the financing against specific eligible expenditures. IPF provides funding for activities that produce the physical/ social infrastructure necessary to reduce poverty and create sustainable development. To create this</t>
+          <t>The OCDS builds on all three of these concepts, and the ultimate goal of the OCDS is to help deliver open contracting using standardized open data. The OCDS describes how to publish data and documents for the procurement of goods, works, and services. It makes contracting data available for anyone to use, modify, and share, for any purpose. The OCDS can be adapted to meet your needs. Whether purchasing medicines, running a municipal recycling program or building an airport, the OCDS helps you organize and publish all relevant data and documents during the process. The OCDS is not an electronic procurement system or database. But it can inform how data is collected, stored and published in these systems. The OCDS can help make sure that the contracting data you collect and publish meet global best practices and are fit-for-purpose to meet the needs of a range of different users. The OCDS helps to increase transparency, enables deeper analysis of contracting data, and facilitates the use of data by a wide range of stakeholders.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://thedocs.worldbank.org/en/doc/caf6a3f677305292d799dbe55fd83bfe-0290012023/original/PROCUREMENT-Beginners-Guide-to-IPF-WEB-VERSION-Nov-2023.pdf</t>
+          <t>https://standard.open-contracting.org/latest/en/primer/what/</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>tender process</t>
+          <t>e-procurement and data standards</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.949</v>
+        <v>0.948</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>1</v>
@@ -1025,36 +1025,36 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>cand_031</t>
+          <t>cand_026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Under what circumstances would an independent contractor not be considered a marketing consultant according to the passage?</t>
+          <t>What is the purpose of a trade agreement?</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>An independent contractor would not be considered a marketing consultant if they provide services that are excluded in subpart 37.2, such as routine engineering and technical services, routine legal, actuarial, auditing, and accounting services, and training services.</t>
+          <t>The purpose of a trade agreement is to facilitate international trade by reducing trade barriers and establishing rules for trade between countries.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>An independent contractor is not a marketing consultant when rendering- (1) Services excluded in subpart  37.2 (2) Routine engineering and technical services (such as installation, operation, or maintenance of systems, equipment, software, components , or facilities); (3) Routine legal, actuarial, auditing, and accounting services; and (4) Training services. 9.502 Applicability. (a) This subpart applies to contracts with either profit or nonprofit organizations, including nonprofit organizations created largely or wholly with Government funds.</t>
+          <t>Wayback Machine United Nations Code for Trade and Transport Locations (UN/LOCODE) International trade Terminology Absolute advantage Balance of payments Balance of trade Capital account Comparative advantage Current account Export-oriented industrialization Fair trade Foreign exchange reserves Globalization Global labor arbitrage Import substitution industrialization Multinational corporation Net capital outflow Outsourcing Tariff Trade justice Trade war Trading nation Organizations and policies International Monetary Fund UN Trade and Development World Bank Group World Trade Organization International Trade Centre International Chamber of Commerce Bilateral investment treaty Economic integration Incoterms ATA Carnet Free-trade zone Special economic zone Trade agreement Trade barrier Trade bloc Political economy Free trade Adam Smith The Wealth of Nations Corn Laws Mercantilism Protectionism Economic nationalism Autarky Dedollarisation Withdrawal from the eurozone Regional organizations Americas Andean Community Caribbean Community Central American Integration System Mercosur Asia-Pacific Association of Southeast Asian Nations Regional Comprehensive Economic Partnership South Asian Association for Regional Cooperation Europe, Central Asia, and North Asia Customs Union of the Eurasian Economic Union Eurasian Economic Union European Union Customs Union Middle East and North Africa Arab Customs Union Gulf Cooperation Council Subsaharan Africa East African Community Economic and Monetary Community of Central Africa Southern African Customs Union West African Economic and Monetary Union Exports by product</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.acquisition.gov/far/part-9</t>
+          <t>https://en.wikipedia.org/wiki/Incoterms</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>supplier evaluation</t>
+          <t>procurement policy and compliance</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.962</v>
+        <v>0.823</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>1</v>
@@ -1063,36 +1063,36 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>cand_032</t>
+          <t>cand_031</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>What journal published the article 'Surging Energy Prices in Europe in the Aftermath of the War: How to Support the Vulnerable and Speed up the Transition Away from Fossil Fuels'?</t>
+          <t>Under what circumstances is an independent contractor not considered a marketing consultant?</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Journal of Cleaner Production</t>
+          <t>An independent contractor is not considered a marketing consultant when rendering services that are excluded in subpart 37.2, routine engineering and technical services (such as installation, operation, or maintenance of systems, equipment, software, components, or facilities), routine legal, actuarial, auditing, and accounting services, and training services.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Review Between 1996 and 2013. Journal of Cleaner Production, 85. Ari, A., Arregui, N., Black, S., Celasun, O., Iakova, D., et al. (2022). Surging Energy Prices in Europe in the Aftermath of the War: How to Support the Vulnerable and Speed up the Transition Away from Fossil Fuels. Barrad, S., Gagnon, S., and Valverde, R. (2020). An An- alytics Architecture for Procurement. International Journal of Information Technologies and Systems Ap-</t>
+          <t>An independent contractor is not a marketing consultant when rendering- (1) Services excluded in subpart  37.2 (2) Routine engineering and technical services (such as installation, operation, or maintenance of systems, equipment, software, components , or facilities); (3) Routine legal, actuarial, auditing, and accounting services; and (4) Training services. 9.502 Applicability. (a) This subpart applies to contracts with either profit or nonprofit organizations, including nonprofit organizations created largely or wholly with Government funds.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://arxiv.org/pdf/2303.03882</t>
+          <t>https://www.acquisition.gov/far/part-9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>e-procurement and data standards</t>
+          <t>supplier evaluation</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.87</v>
+        <v>0.981</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>1</v>
@@ -1101,36 +1101,36 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>cand_033</t>
+          <t>cand_037</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>What are the Borrower's responsibilities in carrying out procurement activities financed by the Bank?</t>
+          <t>What does CFR stand for in international trade?</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>The Borrower is responsible for planning the procurement, preparing a procurement strategy, inviting offers from the market, evaluating offers and determining the Most Advantageous Bid/Proposal, and awarding, signing, and managing contracts. These responsibilities are outlined in the passage as part of the Borrower's role in procurement activities financed by the Bank.</t>
+          <t>CFR stands for Cost and Freight.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>However, several aspects of the Guidance are also relevant for projects subject to the Guidelines. Roles and Responsibilities Borrower The Borrower is responsible for carrying out procurement activities financed by the Bank in accordance with the financing agreement signed between the Bank and the Borrower. In particular, the Borrower must use funds only for the purpose for which they were granted. Other responsibilities include: 1. planning the procurement 2. preparing a procurement strategy for the project, as defined in the Project Procurement Strategy for Development (PPSD) 3. inviting offers from the market 4. evaluating offers and determining the Most Advantageous Bid/Proposal (MABP) 5. awarding, signing, and managing contracts. Bank To ensure that funds are used only for the purpose for which they were granted, the Bank provides Borrowers with procurement implementation support and oversight for each project. Implementation support includes providing training and advice to the Borrower. The Bank conducts its procurement oversight function in order to discharge its fiduciary responsibilities, as required by the Bank’s Articles of Agreement. Prior and Post Reviews This fiduciary responsibility entails the Bank conducting reviews of selected procurement activities</t>
+          <t>, FOB is not only connected with the carriage of goods by sea but also used for inland carriage aboard any "vessel, car or other vehicle." 22 CFR – Cost and Freight (named port of destination) edit The seller pays for the carriage of the goods up to the named port of destination. Risk transfers to buyer when the goods have been loaded on board the ship in the country of Export. The seller is responsible for origin costs including export clearance and freight costs for carriage to the named port. The shipper is not responsible for delivery to the final destination from the port (generally the buyer's facilities), or for buying insurance. If the buyer requires the seller to obtain insurance, the Incoterm CIF should be considered. CFR should only be used for non-containerized seafreight and inland waterway transport; for all other modes of transport it should be replaced with CPT. CIF – Cost, Insurance &amp; Freight (named port of destination) edit Use preceding Incoterms edit</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://thedocs.worldbank.org/en/doc/caf6a3f677305292d799dbe55fd83bfe-0290012023/original/PROCUREMENT-Beginners-Guide-to-IPF-WEB-VERSION-Nov-2023.pdf</t>
+          <t>https://en.wikipedia.org/wiki/Incoterms</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>procurement policy and compliance</t>
+          <t>logistics and KPIs</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.864</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>1</v>
@@ -1139,36 +1139,36 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>cand_034</t>
+          <t>cand_038</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>What are the two main institutions that make up the World Bank?</t>
+          <t>What is the purpose of early consideration of additional sustainable procurement requirements in the procurement process?</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The two main institutions that make up the World Bank are the International Bank for Reconstruction and Development (IBRD) and the International Development Association (IDA).</t>
+          <t>Early consideration of additional sustainable procurement requirements ensures that they are included in the overall procurement approach, which may be designed to consider such requirements at a number of stages of the procurement process, such as prequalification or initial selection of bidders, functional or detailed technical specifications, evaluation criteria, including the use of rated criteria, contract terms and conditions, and contract performance monitoring.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>World Bank The World Bank comprises two WBG institutions, the International Bank for Reconstruction and Development (IBRD), which assists middle-income and creditworthy poorer countries, and the International Development Association (IDA), which focuses on the world’s poorest countries. World Bank Group (WBG) The World Bank Group is a unique global partnership of five institutions working for sustainable solutions that reduce poverty and build shared prosperity in developing countries. The five institutions are the IBRD, IDA, IFC, MIGA, and ICSID. Contents Common Abbreviations and Defined Terms  . . . . . . . . . . . . . . . . . . . . . . . . . . i SECTION I . Introduction  . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 1 Purpose ......................................................................... 1 World Bank Group ................................................................ 1 World Bank ................................................................... 2 Investment Project Financing ....................................................... 3</t>
+          <t>apply additional sustainable Procurement requirements and the manner in which they will be handled in evaluation, such as in the application of Rated Criteria, should be detailed in the PPSD. Early Identification Early consideration of additional sustainable Procurement requirements ensures that they are included in the overall Procurement Approach, which may be designed to consider such requirements at a number of stages of the Procurement Process, such as ◾ Prequalification or Initial Selection of Bidders ◾ Functional or detailed technical specifications ◾ Evaluation Criteria, including the use of Rated Criteria ◾ Contract terms and conditions ◾ Contract performance monitoring.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://thedocs.worldbank.org/en/doc/caf6a3f677305292d799dbe55fd83bfe-0290012023/original/PROCUREMENT-Beginners-Guide-to-IPF-WEB-VERSION-Nov-2023.pdf</t>
+          <t>https://thedocs.worldbank.org/en/doc/a535313d21a71139c93f09311e274093-0290012023/original/Procurement-Guidance-Value-for-Money-Nov-2023-WEB.pdf</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>tender process</t>
+          <t>supplier evaluation</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.618</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>1</v>
@@ -1177,22 +1177,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>cand_035</t>
+          <t>cand_041</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>What must a request for waiver include according to the passage?</t>
+          <t>Under what condition should a contractor not be awarded a contract for evaluating offers in procurement?</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>A request for waiver must be in writing, set forth the extent of the conflict, and require approval by the agency head or a designee.</t>
+          <t>A contractor should not be awarded a contract for evaluating its own offers or those of a competitor without proper safeguards to ensure objectivity and protect the Government’s interests.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9.503 Waiver. The agency head or a designee may waive any general rule or procedure of this subpart by determining that its application in a particular situation would not be in the Government’s interest. Any request for waiver must be in writing shall set forth the extent of the conflict, and requires approval by the agency head or a designee. Agency heads shall not delegate waiver authority below the level of head of a contracting activity 9.504 Contracting officer responsibilities. (a) Using the general rules, procedures, and examples in this subpart, contracting officers shall analyze planned acquisitions in order to- (1) Identify and evaluate potential organizational conflicts of interest as early in the acquisition process as possible; and (2) Avoid, neutralize, or mitigate significant potential conflicts before contract award. (b) Contracting officers should obtain the advice of counsel and the assistance of appropriate technical specialists in evaluating potential conflicts and in developing any necessary solicitation provisions and contract clauses (see 9.506 ). (c) Before issuing a solicitation for a contract that may involve a significant potential conflict, the contracting officer shall recommend to the head of the contracting activity</t>
+          <t>9.505-3 Providing evaluation services. Contracts for the evaluation of offers for products or services shall not be awarded to a contractor that will evaluate its own offers for products or services, or those of a competitor, without proper safeguards to ensure objectivity to protect the Government’s interests. 9.505-4 Obtaining access to proprietary information. (a) When a contractor requires proprietary information from others to perform a Government contract and can use the leverage of the contract to obtain it, the contractor</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1202,11 +1202,11 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>contract management</t>
+          <t>tender process</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.887</v>
+        <v>0.905</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>1</v>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>What should be included in the contract management plan if KPIs are linked to incentive mechanisms or payment decisions?</t>
+          <t>What should KPIs be included in to ensure alignment with the desired outcome in contract management?</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>If KPIs are linked to incentive mechanisms or payment decisions, they will need to be agreed to and included as part of the contract before it is signed.</t>
+          <t>KPIs should be included in the contract management plan.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.948</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>1</v>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>What does viability in supply chains focus on beyond just structural stability and recoverability?</t>
+          <t>What does the term 'viability' refer to in the context of supply chains?</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Viability in supply chains focuses on the ongoing survival and service provision under both acute disruptions and long-term, evolving pressures by integrating resilience with sustainability and adaptive reconfiguration.</t>
+          <t>Viability refers to a supply chain's capability of ongoing survival and service provision under both acute disruptions and long-term, evolving pressures by integrating resilience with sustainability and adaptive reconfiguration.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.945</v>
+        <v>0.926</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>1</v>
@@ -1291,36 +1291,36 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>cand_045</t>
+          <t>cand_044</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>What are some ways to optimize value for money (VfM) in the procurement process according to the passage?</t>
+          <t>What is the difference between the FAS and FOB terms regarding export clearance responsibilities?</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>To optimize value for money (VfM) in the procurement process, the following steps can be taken: ensuring integrity throughout the process, identifying and factoring the needs of end users and other stakeholders, mitigating risks through the design of procurement arrangements, ensuring that procurement arrangements are fit for purpose, providing opportunities for cost-effective and innovative solutions, and basing contract award decisions on suitable evaluation criteria. These steps help to effectively, efficiently, and economically use the resources available to a project.</t>
+          <t>The FAS term requires the seller to clear the goods for export, which is a reversal from previous Incoterms versions that required the buyer to arrange for export clearance. However, if the parties wish the buyer to clear the goods for export, this should be made clear by adding explicit wording to this effect in the contract of sale.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Optimizing VfM The Procurement Process includes numerous opportunities to address VfM. This supports develop- ing a fit-for-purpose Procurement Approach that is both country and project specific. Figure I demonstrates that VfM elements can be individual and cumulative and exist throughout the Procurement Process to more effectively, efficiently, and economically use the resources available to a project, in other words, to optimize VfM. Examples include ensuring: ◾ Integrity throughout the Procurement Process ◾ That the needs of end users and other stakeholders are appropriately identified and factored into the Procurement Arrangements ◾ That risks to achieving the required objectives are appropriately identified and mitigated through design of the Procurement Arrangements ◾ That the Procurement Arrangements are fit for purpose relative to the risk, value, and complex- ity of the Procurement and to the operating context and nature of the supply market ◾ When appropriate, that providers are given the opportunity to offer cost-effective and innova- tive solutions to meet identified needs ◾ That contract award decisions are based on suitable Evaluation Criteria and when appropriate the use of Rated Criteria</t>
+          <t>The FAS term requires the seller to clear the goods for export, which is a reversal from previous Incoterms versions that required the buyer to arrange for export clearance. However, if the parties wish the buyer to clear the goods for export, this should be made clear by adding explicit wording to this effect in the contract of sale. This term should be used only for non-containerized sea freight and inland waterway transport. FOB – Free on Board (named port of shipment) edit Main article: FOB (Shipping) Under FOB terms the seller bears all costs and risks up to the point the goods are loaded on board the vessel. The seller's responsibility does not end at that point unless the goods are "appropriated to the contract" that is, they are "clearly set aside or otherwise identified as the contract goods".</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://thedocs.worldbank.org/en/doc/a535313d21a71139c93f09311e274093-0290012023/original/Procurement-Guidance-Value-for-Money-Nov-2023-WEB.pdf</t>
+          <t>https://en.wikipedia.org/wiki/Incoterms</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>supplier evaluation</t>
+          <t>logistics and KPIs</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>1</v>
@@ -1329,22 +1329,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>cand_048</t>
+          <t>cand_045</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>What factors influence the choice of selection method for each contract?</t>
+          <t>What is the purpose of addressing VfM elements in the procurement process?</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>The choice of selection method for each contract is influenced by the capacity and level of competition in the market, the number of qualified bidders available, the specificity, complexity, and nature of the procurement requirement, and the inherent risks involved in the contract, as well as how these risks may best be mitigated through the procurement process and resulting contract.</t>
+          <t>The purpose of addressing VfM elements in the procurement process is to more effectively, efficiently, and economically use the resources available to a project, in other words, to optimize VfM.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Bid or Proposal for each contract. The choice of selection method to be used for each contract is driven by a number of factors: ◾ Primarily by the capacity and level of competition in the market ◾ Number of qualified Bidders available ◾ Specificity, complexity, and nature of the Procurement requirement ◾ Inherent risks involved in the contract, as well as how the identified risks may best be mitigated through the Procurement Process and resulting contract. Each combination of options will present a different trade-off between costs and benefits. VALUE FOR MONEY: ACHIEVING VfM IN INVESTMENT PROJECTS FINANCED BY THE WORLD BANK</t>
+          <t>Optimizing VfM The Procurement Process includes numerous opportunities to address VfM. This supports develop- ing a fit-for-purpose Procurement Approach that is both country and project specific. Figure I demonstrates that VfM elements can be individual and cumulative and exist throughout the Procurement Process to more effectively, efficiently, and economically use the resources available to a project, in other words, to optimize VfM. Examples include ensuring: ◾ Integrity throughout the Procurement Process ◾ That the needs of end users and other stakeholders are appropriately identified and factored into the Procurement Arrangements ◾ That risks to achieving the required objectives are appropriately identified and mitigated through design of the Procurement Arrangements ◾ That the Procurement Arrangements are fit for purpose relative to the risk, value, and complex- ity of the Procurement and to the operating context and nature of the supply market ◾ When appropriate, that providers are given the opportunity to offer cost-effective and innova- tive solutions to meet identified needs ◾ That contract award decisions are based on suitable Evaluation Criteria and when appropriate the use of Rated Criteria</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1354,11 +1354,11 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>tender process</t>
+          <t>supplier evaluation</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.766</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>1</v>
@@ -1367,36 +1367,36 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>cand_049</t>
+          <t>cand_048</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>What is WSLA and what does it allow authors to specify?</t>
+          <t>What factors influence the choice of selection method for a contract in procurement?</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>WSLA is a standard for service level agreement compliance monitoring of web services. It allows authors to specify the performance metrics associated with a web service application, desired performance targets, and actions that should be performed when performance is not met.</t>
+          <t>The choice of selection method for a contract is influenced by several factors, including the capacity and level of competition in the market, the number of qualified bidders available, the specificity, complexity, and nature of the procurement requirement, and the inherent risks involved in the contract, as well as how these risks may be mitigated through the procurement process and resulting contract.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10 Fixed networks edit For fixed networks subscribers, service modeling appears to be one of the most suitable ways to effectively monitor SLA's and ensure they are met. 11 WSLA edit web service level agreement WSLA ) is a standard for service level agreement compliance monitoring of web services . It allows authors to specify the performance metrics associated with a web service application, desired performance targets, and actions that should be performed when performance is not met. WSLA Language Specification, version 1.0 12 was published by IBM in 2001. Cloud computing edit The underlying benefit of cloud computing is shared resources, which are supported by the underlying nature of a shared infrastructure environment. Thus, SLAs span across the cloud and are offered by service providers as a service-based agreements rather than a customer-based agreements. Measuring, monitoring and reporting on cloud performance is based on the end UX or their ability to consume resources. The downside of cloud computing relative to SLAs is the difficulty in determining the root cause of service interruptions due to the complex nature of the environment.</t>
+          <t>Bid or Proposal for each contract. The choice of selection method to be used for each contract is driven by a number of factors: ◾ Primarily by the capacity and level of competition in the market ◾ Number of qualified Bidders available ◾ Specificity, complexity, and nature of the Procurement requirement ◾ Inherent risks involved in the contract, as well as how the identified risks may best be mitigated through the Procurement Process and resulting contract. Each combination of options will present a different trade-off between costs and benefits. VALUE FOR MONEY: ACHIEVING VfM IN INVESTMENT PROJECTS FINANCED BY THE WORLD BANK</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Service-level_agreement</t>
+          <t>https://thedocs.worldbank.org/en/doc/a535313d21a71139c93f09311e274093-0290012023/original/Procurement-Guidance-Value-for-Money-Nov-2023-WEB.pdf</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>contract management</t>
+          <t>tender process</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.926</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>1</v>
@@ -1405,36 +1405,36 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>cand_050</t>
+          <t>cand_049</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>What was the main objective of the sustainable public procurement project in France?</t>
+          <t>What is the purpose of a web service level agreement (WSLA)?</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>The main objective of the sustainable public procurement project in France was toner cartridges for laser printers.</t>
+          <t>A web service level agreement (WSLA) is a standard for service level agreement compliance monitoring of web services. It allows authors to specify the performance metrics associated with a web service application, desired performance targets, and actions that should be performed when performance is not met.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>21 Case studies edit The Marrakech Task Force on Sustainable Public Procurement (MTF or SPP) which was managed by Switzerland from 2006 to May 2011 established an approach for the effective implementation of sustainable procurement. This approach was named the MTF Approach to SPP. Since then, the United Nations Environmental Programme have worked together with the Swiss government to develop a project to implement sustainable procurement worldwide. The project named Capacity Building for Sustainable Public Procurement in Developing Countries was piloted in seven countries: Chile, Colombia, Costa Rica, Lebanon, Mauritius, Tunisia, and Uruguay. Since then, the list of countries adopting this newly designed approach to developing has increased, adding more advanced and industrialized nations to be used as case studies to measure the efficiency and benefits of the implementation of sustainable public procurement. In Brazil, the project involved recycled paper; in Costa Rica, the management services was redesigned; toner cartridges for laser printers were the main objective in France; in Hong Kong and China the nations aimed to improve traffic with LED traffic light retrofitting; organic food for school children was the focus in Italy; sustainable construction was the focus in England; consultancy and temporary staff services were renovated in Scotland; and in the United States, there was a push for the sustainable transportation of waste.</t>
+          <t>10 Fixed networks edit For fixed networks subscribers, service modeling appears to be one of the most suitable ways to effectively monitor SLA's and ensure they are met. 11 WSLA edit web service level agreement WSLA ) is a standard for service level agreement compliance monitoring of web services . It allows authors to specify the performance metrics associated with a web service application, desired performance targets, and actions that should be performed when performance is not met. WSLA Language Specification, version 1.0 12 was published by IBM in 2001. Cloud computing edit The underlying benefit of cloud computing is shared resources, which are supported by the underlying nature of a shared infrastructure environment. Thus, SLAs span across the cloud and are offered by service providers as a service-based agreements rather than a customer-based agreements. Measuring, monitoring and reporting on cloud performance is based on the end UX or their ability to consume resources. The downside of cloud computing relative to SLAs is the difficulty in determining the root cause of service interruptions due to the complex nature of the environment.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sustainable_procurement</t>
+          <t>https://en.wikipedia.org/wiki/Service-level_agreement</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>risk and sustainability</t>
+          <t>contract management</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.887</v>
+        <v>0.929</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>1</v>
@@ -1569,22 +1569,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cand_002</t>
+          <t>cand_001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>What does TTR stand for and what does it measure in the context of supply chain disruptions?</t>
+          <t>What are some options to manage supply chain risks?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>TTR stands for Time To Recovery, which measures the time it takes a company to restore full operational output following a major supply chain disruption.</t>
+          <t>Some options to manage supply chain risks include addressing sourcing risks as an integral part of the product design and engineering, managing stock levels, considering alternative sourcing and flexible logistical arrangements, using general purpose contingency arrangements such as business interruption insurance and proactive business relationship management, supplier questionnaires, risk assessments, audits, and certification, awareness campaigns and training programs, using business intelligence from big data analytics and continuous monitoring, optimizing redundancy, and implementing comprehensive digitalization and modernization of management methods.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>12 TTR measures the time it takes a company to restore full operational output following a major supply chain disruption. The determination of TTR assumes that a facility is essentially unusable due to a major event, requiring extensive repairs and reconstruction, as well as re-sourcing and re-qualifying of key equipment used in manufacturing and other operations. In essence, Time To Recovery is a measure of how long it would take a supply chain to return to normal after suffering</t>
+          <t>25 Supply chain resilience options edit Some options to engineer an acceptable risk level in supply chains include: Addressing sourcing risks as an integral part of the product design and engineering (e.g. preferring standardized multi-sourced commodities over custom or unique supplies from sole suppliers) Managing stock levels both statically and dynamically Considering alternative sourcing and flexible logistical arrangements (e.g. trucks to supplement or replace trains) General purpose contingency arrangements such as business interruption insurance and proactive business relationship management (building mutual understanding and trust) Supplier questionnaires, risk assessments, audits and certification, both for initial supplier selection and subsequently (e.g. refreshed prior to major changes such as new products, or in response to issues arising) Awareness campaigns and training programs The use of business intelligence from big data analytics and continuous monitoring for predictive security measures vs. clean up Redundancy optimization (e.g. focusing redundancy efforts on business- or mission-critical products) Slick incident management where time is of the essence Postponement, product substitution and other forms of downstream supply chain management (assisting customers) Comprehensive digitalization and modernization of management methods</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1594,11 +1594,11 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>logistics and KPIs</t>
+          <t>risk and sustainability</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.944</v>
+        <v>0.953</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1</v>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12 TTR measures the time it takes a company to restore full operational output following a major supply chain disruption.</t>
+          <t>Some options to engineer an acceptable risk level in supply chains include: Addressing sourcing risks as an integral part of the product design and engineering (e.g. preferring standardized multi-sourced commodities over custom or unique supplies from sole suppliers) Managing stock levels both statically and dynamically Considering alternative sourcing and flexible logistical arrangements (e.g. trucks to supplement or replace trains) General purpose contingency arrangements such as business interruption insurance and proactive business relationship management (building mutual understanding and trust) Supplier questionnaires, risk assessments, audits and certification, both for initial supplier selection and subsequently (e.g. refreshed prior to major changes such as new products, or in response to issues arising) Awareness campaigns and training programs The use of business intelligence from big data analytics and continuous monitoring for predictive security measures vs. clean up Redundancy optimization (e.g. focusing redundancy efforts on business- or mission-critical products) Slick incident management where time is of the essence Postponement, product substitution and other forms of downstream supply chain management (assisting customers) Comprehensive digitalization and modernization of management methods</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -1642,55 +1642,55 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>wikipedia_supplier_risk::c005</t>
+          <t>wikipedia_supplier_risk::c013</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cand_004</t>
+          <t>cand_002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Why do Pekša and Grabis suggest decoupling decision-making logic from ERP systems in their research?</t>
+          <t>What does TTR measure in the context of supply chain management?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Pekša and Grabis suggest decoupling decision-making logic from ERP systems because decision-making techniques should be modifiable, scalable, and portable. This decoupling enables the usage of advanced decision-making techniques, whereas implementing decision-making directly into existing ERP systems is seen as inflexible and cost-intensive, leading to competitive disadvantages.</t>
+          <t>TTR measures the time it takes a company to restore full operational output following a major supply chain disruption.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>tologies and propose an integration framework based on ontology learning including a basic workﬂow (Ma and Moln´ar, 2019). Pekˇsa and Grabis (Pekˇsa and Gra- bis, 2018) reviewed existing research on the decision- making capabilities of ERP systems. They identiﬁed different approaches for integrating decision-making logic for companies. Since decision-making tech- niques should be modiﬁable, scalable, and portable, they suggest decoupling decision-making logic from ERP systems. This decoupling enables the usage of advanced decision-making techniques. Implementing decision-making directly into existing ERP systems is seen as inﬂexible and cost-intensive, leading to com- petitive disadvantages. In the last years, many articles regarding SCM and procurement are published. For example, Re- jeb et al. (Rejeb et al., 2018) outline the potential of new technologies like Big Data analysis, Automatiza- tion and Robotics, IoT, and Blockchain Technology in procurement-related work since the entire supply chain has already and will continue to have techno- logical shifts. Nevertheless, the article does not fo- cus on ERP systems. However, Tarigan et al. (Tarigan</t>
+          <t>12 TTR measures the time it takes a company to restore full operational output following a major supply chain disruption. The determination of TTR assumes that a facility is essentially unusable due to a major event, requiring extensive repairs and reconstruction, as well as re-sourcing and re-qualifying of key equipment used in manufacturing and other operations. In essence, Time To Recovery is a measure of how long it would take a supply chain to return to normal after suffering</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://arxiv.org/pdf/2303.03882</t>
+          <t>https://en.wikipedia.org/wiki/Supply_chain_risk_management</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>e-procurement and data standards</t>
+          <t>logistics and KPIs</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.903</v>
+        <v>0.953</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>analytical</t>
+          <t>factual</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
@@ -1707,65 +1707,65 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Since decision-making tech- niques should be modiﬁable, scalable, and portable, they suggest decoupling decision-making logic from ERP systems. This decoupling enables the usage of advanced decision-making techniques. Implementing decision-making directly into existing ERP systems is seen as inﬂexible and cost-intensive, leading to com- petitive disadvantages.</t>
+          <t>12 TTR measures the time it takes a company to restore full operational output following a major supply chain disruption.</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>arXiv.org perpetual non-exclusive license (open access)</t>
+          <t>CC BY-SA 4.0</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>arxiv_digital_procurement</t>
+          <t>wikipedia_supplier_risk</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>arxiv_digital_procurement::c008</t>
+          <t>wikipedia_supplier_risk::c005</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>cand_005</t>
+          <t>cand_006</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>What method does the passage suggest for assessing the effectiveness of public procurement plans?</t>
+          <t>What are monetarily quantifiable criteria in procurement evaluation?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>The passage suggests conducting interviews with procurers to assess the degree of training and knowledge, as well as recognizing and understanding the obstacles in the implementation of SPP in their respective administration.</t>
+          <t>Monetarily quantifiable criteria in procurement evaluation are factors that can be measured in monetary terms and are specified in the Procurement Documents to determine the evaluated financial cost of each Bid/Proposal. Examples include margin of domestic preference, time schedule adjustment, payment schedule adjustment, life-cycle costing, functional guarantees min/max adjustment, and adjustments for nonmaterial non-conformities.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11 Project set up and governance structure establishment In the project organization and set up in pilot country of Mauritius, the NFO (Mauritius public procurement office) set up monthly and biweekly newsletters on the purpose of public procurement which was then used as a communication device for later projects, activities, and events, along with other relevant information 21 Assessment, review, and prioritization Recommended method of assessing the effectiveness of public procurement plans is conducting interviews with procurers as to assess the degree of training and knowledge. Recognize and understand the obstacles in the implementation of SPP in their respective administration as well as identifying products and services which are considered a priority for the well-functioning of such projects and policies.</t>
+          <t>There are two main types of evaluation and qualification criteria. a. Monetarily quantifiable criteria When setting monetarily quantifiable Evaluation Criteria, the Procurement Documents shall specify the relevant factors to be considered in the Bid/Proposal evaluation and the manner in A BEGINNER’S GUIDE FOR BORROWERS: PROCUREMENT UNDER WORLD BANK INVESTMENT PROJECT FINANCING 24 which they will be applied for the purpose of determining the evaluated financial cost of each Bid/Proposal. Examples of where monetarily quantifiable criteria may be applied to determine the total eval- uated Bid/Proposal financial cost may include, among others: i. margin of domestic preference (if agreed with the Bank) ii.  time schedule adjustment iii.  payment schedule adjustment iv.  life-cycle costing v.  functional guarantees min/max adjustment vi.  adjustments for nonmaterial non-conformities</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sustainable_procurement</t>
+          <t>https://thedocs.worldbank.org/en/doc/caf6a3f677305292d799dbe55fd83bfe-0290012023/original/PROCUREMENT-Beginners-Guide-to-IPF-WEB-VERSION-Nov-2023.pdf</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>procurement policy and compliance</t>
+          <t>tender process</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.834</v>
+        <v>0.822</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>analytical</t>
+          <t>factual</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1774,71 +1774,71 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>5</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Recommended method of assessing the effectiveness of public procurement plans is conducting interviews with procurers as to assess the degree of training and knowledge. Recognize and understand the obstacles in the implementation of SPP in their respective administration</t>
+          <t>When setting monetarily quantifiable Evaluation Criteria, the Procurement Documents shall specify the relevant factors to be considered in the Bid/Proposal evaluation and the manner in which they will be applied for the purpose of determining the evaluated financial cost of each Bid/Proposal. Examples of where monetarily quantifiable criteria may be applied to determine the total evaluated Bid/Proposal financial cost may include, among others: i. margin of domestic preference (if agreed with the Bank) ii. time schedule adjustment iii. payment schedule adjustment iv. life-cycle costing v. functional guarantees min/max adjustment vi. adjustments for nonmaterial non-conformities</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>CC BY-SA 4.0</t>
+          <t>CC BY 3.0 IGO (World Bank open access)</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>wikipedia_green_proc</t>
+          <t>worldbank_beginners_guide</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>wikipedia_green_proc::c013</t>
+          <t>worldbank_beginners_guide::c062</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>cand_006</t>
+          <t>cand_007</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>What are some examples of monetarily quantifiable criteria that can be used to determine the total evaluated Bid/Proposal financial cost?</t>
+          <t>What does the term 'indictment' mean in the context of procurement regulations?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Examples of monetarily quantifiable criteria include the margin of domestic preference, time schedule adjustment, payment schedule adjustment, life-cycle costing, functional guarantees min/max adjustment, and adjustments for nonmaterial non-conformities.</t>
+          <t>The term 'indictment' means indictment for a criminal offense. An information or other filing by competent authority charging a criminal offense is given the same effect as an indictment.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>There are two main types of evaluation and qualification criteria. a. Monetarily quantifiable criteria When setting monetarily quantifiable Evaluation Criteria, the Procurement Documents shall specify the relevant factors to be considered in the Bid/Proposal evaluation and the manner in A BEGINNER’S GUIDE FOR BORROWERS: PROCUREMENT UNDER WORLD BANK INVESTMENT PROJECT FINANCING 24 which they will be applied for the purpose of determining the evaluated financial cost of each Bid/Proposal. Examples of where monetarily quantifiable criteria may be applied to determine the total eval- uated Bid/Proposal financial cost may include, among others: i. margin of domestic preference (if agreed with the Bank) ii.  time schedule adjustment iii.  payment schedule adjustment iv.  life-cycle costing v.  functional guarantees min/max adjustment vi.  adjustments for nonmaterial non-conformities</t>
+          <t>(2) Conducts business, or reasonably may be expected to conduct business, with the Government as an agent or representative of another contractor Indictment means indictment for a criminal offense. An information or other filing by competent authority charging a criminal offense is given the same effect as an indictment Legal proceedings means any civil judicial proceeding to which the Government is a party or any criminal proceeding. The term includes appeals from such proceedings. Nonprocurement Common Rule means the procedures used by Federal Executive Agencies to suspend, debar, or exclude individuals or entities from participation in nonprocurement transactions under Executive Order 12549. Examples of nonprocurement transactions are grants, cooperative agreements, scholarships, fellowships, contracts of assistance, loans, loan guarantees, subsidies, insurance , payments for specified use, and donation agreements. See 2 CFR part 180 and agency enacting regulations in 2 CFR subtitle B Pre-notice letter means a written correspondence issued to a contractor in a suspension or debarment matter, which does not immediately result in an exclusion or ineligibility. The letter is issued at the discretion of the suspending and debarring official</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://thedocs.worldbank.org/en/doc/caf6a3f677305292d799dbe55fd83bfe-0290012023/original/PROCUREMENT-Beginners-Guide-to-IPF-WEB-VERSION-Nov-2023.pdf</t>
+          <t>https://www.acquisition.gov/far/part-9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>tender process</t>
+          <t>contract management</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.619</v>
+        <v>0.844</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1</v>
@@ -1850,11 +1850,11 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.612</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>5</v>
@@ -1867,22 +1867,22 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Examples of where monetarily quantifiable criteria may be applied to determine the total evaluated Bid/Proposal financial cost may include, among others: i. margin of domestic preference (if agreed with the Bank) ii. time schedule adjustment iii. payment schedule adjustment iv. life-cycle costing v. functional guarantees min/max adjustment vi. adjustments for nonmaterial non-conformities</t>
+          <t>Indictment means indictment for a criminal offense. An information or other filing by competent authority charging a criminal offense is given the same effect as an indictment</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>CC BY 3.0 IGO (World Bank open access)</t>
+          <t>US Government public domain</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>worldbank_beginners_guide</t>
+          <t>far_part9_qualifications</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>worldbank_beginners_guide::c062</t>
+          <t>far_part9_qualifications::c104</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>What should sustainable procurement requirements be based on according to the passage?</t>
+          <t>What should sustainable procurement requirements be based on?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1969,43 +1969,43 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>cand_011</t>
+          <t>cand_010</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>What are some benefits of following OCDS rules and guidance when publishing contracting data?</t>
+          <t>What is the purpose of incorporating supply chain considerations in the works requirements/specification?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Following OCDS rules and guidance will help you and your users to access clear definitions for the meaning, structure, and format of your data, access a growing ecosystem of reusable tools and methodologies for working with OCDS data, compare your data with other publishers' data to examine value for money and other types of analysis, and check the structure, format, and quality of your data against the OCDS schema.</t>
+          <t>Incorporating supply chain considerations in the works requirements/specification can be a critical element that influences the success of the relationship between the parties and how future supply chain challenges are managed. Borrowers should consider the Project Development Objectives and the VfM principles when drafting the works requirements/specification (and the final contract), and design them with a “fit for purpose” mindset, that is to say, one that is proportionate to the complexity, risk, and value of the procurement.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>While JSON is the default format, a good publication will publish tabular formats as well both so that more usersâ needs can be satisfied. No matter what type of contracting data you are working with or format you publish in, following OCDS rules and guidance will help you and your users to: Access clear definitions for the meaning, structure and format of your data Access a growing ecosystem of reusable tools and methodologies for working with OCDS data Compare your data with other publishersâ data to examine value for money and other types of analysis Check the structure, format and quality of your data against the OCDS schema Note To learn more, go to the next page in the Primer: How is OCDS data published? You can also review the further resources below to go deeper into the subjects introduced on this page. Guidance to implementing OCDS Video Learning Guide to the OCDS OCP Learning: Publishing OCDS Data Open Contracting Playbook: Component 2</t>
+          <t>Is the evidence required proportionate to the risks? ☐ Yes ☐ No Can the terms and conditions of the contract address these risks? ☐ Yes ☐ No Do the terms and conditions pass unnecessary risks to the Supplier/Contractor? ☐ Yes ☐ No Including Supply Chain Considerations in the Works Requirements/Specification The Bank’s SPDs include general provisions related to SCM. While the Bank does not allow a Borrower to adjust standard contract terms in SPDs, additional supply chain considerations can be addressed in the Works requirements/specification. Including such SCM considerations can be a critical element that influences the success of the relationship between the parties and how future SCM challenges are managed. Borrowers should therefore consider the Project Development Objectives and the VfM principles when drafting the Works requirements/specification (and the final contract), and design them with a “fit for purpose” mindset, that is to say, one that is proportionate to the complexity, risk, and value of the procurement. Where appropriate, Borrowers should include in the Works requirements/specification additional SCM expectations for Suppliers/Contractors, which can spell out further SCM requirements that</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://standard.open-contracting.org/latest/en/getting_started/building_blocks/</t>
+          <t>https://thedocs.worldbank.org/en/doc/1c3b517f003b53a2e2e170e93124be84-0290032023/original/World-Bank-Supply-Chain-Management-Guidance.pdf</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>e-procurement and data standards</t>
+          <t>supplier evaluation</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.92</v>
+        <v>0.929</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>analytical</t>
+          <t>factual</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2017,68 +2017,68 @@
         <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>5</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Following OCDS rules and guidance will help you and your users to: Access clear definitions for the meaning, structure and format of your data Access a growing ecosystem of reusable tools and methodologies for working with OCDS data Compare your data with other publishersâ data to examine value for money and other types of analysis Check the structure, format and quality of your data against the OCDS schema</t>
+          <t>Including such SCM considerations can be a critical element that influences the success of the relationship between the parties and how future SCM challenges are managed. Borrowers should therefore consider the Project Development Objectives and the VfM principles when drafting the Works requirements/specification (and the final contract), and design them with a “fit for purpose” mindset, that is to say, one that is proportionate to the complexity, risk, and value of the procurement.</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>CC-BY (Open Contracting Partnership)</t>
+          <t>CC BY 3.0 IGO (World Bank open access)</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>ocds_building_blocks</t>
+          <t>worldbank_supply_chain_mgmt</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>ocds_building_blocks::c005</t>
+          <t>worldbank_supply_chain_mgmt::c139</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>cand_012</t>
+          <t>cand_011</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>What types of national legislation might impact supply chain management in a project?</t>
+          <t>What benefits does following OCDS rules and guidance provide to data publishers and users?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>National legislation might impact supply chain management by requiring environmental and social risk assessments, specifying land use processes, setting obligations related to biodiversity, and imposing specific requirements for stakeholder engagement and emission levels. For example, national legislation may require carrying out environmental and social risk assessments for proposed projects.</t>
+          <t>Following OCDS rules and guidance helps data publishers and users to access clear definitions for the meaning, structure, and format of their data, access a growing ecosystem of reusable tools and methodologies for working with OCDS data, compare their data with other publishers' data to examine value for money and other types of analysis, and check the structure, format, and quality of their data against the OCDS schema.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>hensive labor legislation, covering terms and conditions of work, occupational health and safety, and protection for vulnerable groups. National legislation may include requirements to carry out environ- mental and social risk assessments for proposed projects; specify processes for use of land or land acquisition; set out obligations relating to biodiversity; or have specific requirements for engagement and consultation with different stakeholders. There can also be specific requirements for maximum emission levels, quality of water discharge, and noise levels. In addition to national legislation, there may also be regional and local legislation that needs to be adhered to. Governments may also be subject to different international agreements or conventions, which apply when a government is a party or has ratified these, that are relevant to SCM for the proposed project. Examples41 include the ILO Labor Standards, the Paris Agreement, the Aarhus Convention, the Convention on Biological Diversity, the Convention on Migratory Species, and the World Heritage Convention. ANNEX SUPPL Y CHAIN MANAGEMENT: AN INTRODUCTION AND PRACTICAL TOOLSET FOR PROCUREMENT PRACTITIONERS</t>
+          <t>While JSON is the default format, a good publication will publish tabular formats as well both so that more usersâ needs can be satisfied. No matter what type of contracting data you are working with or format you publish in, following OCDS rules and guidance will help you and your users to: Access clear definitions for the meaning, structure and format of your data Access a growing ecosystem of reusable tools and methodologies for working with OCDS data Compare your data with other publishersâ data to examine value for money and other types of analysis Check the structure, format and quality of your data against the OCDS schema Note To learn more, go to the next page in the Primer: How is OCDS data published? You can also review the further resources below to go deeper into the subjects introduced on this page. Guidance to implementing OCDS Video Learning Guide to the OCDS OCP Learning: Publishing OCDS Data Open Contracting Playbook: Component 2</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://thedocs.worldbank.org/en/doc/1c3b517f003b53a2e2e170e93124be84-0290032023/original/World-Bank-Supply-Chain-Management-Guidance.pdf</t>
+          <t>https://standard.open-contracting.org/latest/en/getting_started/building_blocks/</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>procurement policy and compliance</t>
+          <t>e-procurement and data standards</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.899</v>
+        <v>0.63</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1</v>
@@ -2094,71 +2094,71 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1</v>
+        <v>0.595</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>5</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>National legislation may include requirements to carry out environ- mental and social risk assessments for proposed projects; specify processes for use of land or land acquisition; set out obligations relating to biodiversity; or have specific requirements for engagement and consultation with different stakeholders.</t>
+          <t>Following OCDS rules and guidance will help you and your users to: Access clear definitions for the meaning, structure and format of your data Access a growing ecosystem of reusable tools and methodologies for working with OCDS data Compare your data with other publishers' data to examine value for money and other types of analysis Check the structure, format and quality of your data against the OCDS schema</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>CC BY 3.0 IGO (World Bank open access)</t>
+          <t>CC-BY (Open Contracting Partnership)</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>worldbank_supply_chain_mgmt</t>
+          <t>ocds_building_blocks</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>worldbank_supply_chain_mgmt::c204</t>
+          <t>ocds_building_blocks::c005</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>cand_014</t>
+          <t>cand_012</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Under what circumstances can a debarment be extended for an additional period of one year?</t>
+          <t>What does national legislation typically cover in the context of supply chain management?</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>A debarment can be extended for an additional period of one year if the Secretary of Homeland Security or the Attorney General determines that the contractor continues to be in violation of the employment provisions of the Immigration and Nationality Act.</t>
+          <t>National legislation typically covers terms and conditions of work, occupational health and safety, and protection for vulnerable groups. It may also include requirements for environmental and social risk assessments, processes for land use or acquisition, obligations related to biodiversity, and specific requirements for stakeholder engagement and consultation.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>not be extended solely on the basis of the facts and circumstances upon which the initial debarment action was based. Debarments under 9.406-2 (b)(2) may be extended for additional periods of one year if the Secretary of Homeland Security or the Attorney General determines that the contractor continues to be in violation of the employment provisions of the Immigration and Nationality Act. If debarment for an additional period is determined to be necessary, the procedures of</t>
+          <t>hensive labor legislation, covering terms and conditions of work, occupational health and safety, and protection for vulnerable groups. National legislation may include requirements to carry out environ- mental and social risk assessments for proposed projects; specify processes for use of land or land acquisition; set out obligations relating to biodiversity; or have specific requirements for engagement and consultation with different stakeholders. There can also be specific requirements for maximum emission levels, quality of water discharge, and noise levels. In addition to national legislation, there may also be regional and local legislation that needs to be adhered to. Governments may also be subject to different international agreements or conventions, which apply when a government is a party or has ratified these, that are relevant to SCM for the proposed project. Examples41 include the ILO Labor Standards, the Paris Agreement, the Aarhus Convention, the Convention on Biological Diversity, the Convention on Migratory Species, and the World Heritage Convention. ANNEX SUPPL Y CHAIN MANAGEMENT: AN INTRODUCTION AND PRACTICAL TOOLSET FOR PROCUREMENT PRACTITIONERS</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.acquisition.gov/far/part-9</t>
+          <t>https://thedocs.worldbank.org/en/doc/1c3b517f003b53a2e2e170e93124be84-0290032023/original/World-Bank-Supply-Chain-Management-Guidance.pdf</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>contract management</t>
+          <t>procurement policy and compliance</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.98</v>
+        <v>0.907</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1</v>
@@ -2187,44 +2187,44 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Debarments under 9.406-2 (b)(2) may be extended for additional periods of one year if the Secretary of Homeland Security or the Attorney General determines that the contractor continues to be in violation of the employment provisions of the Immigration and Nationality Act.</t>
+          <t>National legislation may include requirements to carry out environ- mental and social risk assessments for proposed projects; specify processes for use of land or land acquisition; set out obligations relating to biodiversity; or have specific requirements for engagement and consultation with different stakeholders.</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>US Government public domain</t>
+          <t>CC BY 3.0 IGO (World Bank open access)</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>far_part9_qualifications</t>
+          <t>worldbank_supply_chain_mgmt</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>far_part9_qualifications::c152</t>
+          <t>worldbank_supply_chain_mgmt::c204</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>cand_017</t>
+          <t>cand_013</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>What does SCM stand for and what does it refer to?</t>
+          <t>What is the purpose of a procurement approach in the context of project development?</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>SCM stands for Supply Chain Management, which refers to the coordination of activities needed to provide a final product or service. These activities start with the raw materials and end with the delivery of the final product or service to the end customer. At the end of the product or asset’s usable life, supply chains are also responsible for coordinating the recycling, remanufacturing, or disposal of the final product.</t>
+          <t>The purpose of a procurement approach is to award contracts that deliver the Project Development Objectives and Value for Money. This includes the procurement arrangements, procurement risk management, contract strategy, market engagement, requirements drafting, and contract management (where appropriate).</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Develop strategy Assess the market and operating environment and determine procurement approach (PPSD). Invite oﬀers Request oﬀers from the market e.g. RFS or RFP. Answer questions from the market. Evaluate oﬀers Compare oﬀers and determine most advantageous bid/proposal. Manage contract Finalize Contract Management Plan and implement monitoring, evaluation and payment systems. Ensure both parties meet their obligations. 02 04 06 01 03 05 07 FIGURE I The Bank’s procurement process What is Supply Chain Management? SCM refers to the coordination of activities needed to provide a final product or service. These activ- ities start with the raw materials and end with the delivery of the final product or service to the end customer. At the end of the product or asset’s usable life, supply chains are also responsible for coor- dinating the recycling, remanufacturing (i.e., the rebuilding of a product to its original specifications SECTION I: INTRODUCTION using reused parts), or disposal of the final product. The supply chain captures all Organizations and activities that are responsible for or can influence this process, including Suppliers/Contractors, logistics Organizations, and governmental agencies (e.g., customs). Understanding and managing the supply chain is important for Borrowers procuring goods from Manu-</t>
+          <t>development objectives of the project and deliver VfM. iii COMMON ABBREVIATIONS AND DEFINED TERMS Abbreviation/term Full terminology/definition Prequalification The shortlisting process which can be used prior to inviting Request for Bids in the procurement of Goods, Works or Non-consulting Services. Procurement Approach Procurement approach is the overall design of “fit for purpose” procurement to award contracts that deliver the Project Development Objectives and Value for Money. This includes the procurement arrangements, procurement risk management, contract strategy, market engagement, requirements drafting and contract management (where appropriate). Project Development Objectives Project Development Objectives (PDOs) are set out in the approved Project Concept Note and are considered mandatory unless analysis demonstrates the need for adjustment. Procurement Documents A generic term used to cover all Procurement Documents issued by the Borrower soliciting applications/Bids/Proposals. Procurement Documents include prequalification document, initial selection document, Request for Bids document, Request for Proposal document, forms of contracts, and</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2234,11 +2234,11 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>supplier evaluation</t>
+          <t>tender process</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.606</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1</v>
@@ -2250,11 +2250,11 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.525</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>5</v>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>SCM refers to the coordination of activities needed to provide a final product or service. These activ- ities start with the raw materials and end with the delivery of the final product or service to the end customer. At the end of the product or asset’s usable life, supply chains are also responsible for coor- dinating the recycling, remanufacturing (i.e., the rebuilding of a product to its original specifications using reused parts), or disposal of the final product.</t>
+          <t>Procurement approach is the overall design of “fit for purpose” procurement to award contracts that deliver the Project Development Objectives and Value for Money. This includes the procurement arrangements, procurement risk management, contract strategy, market engagement, requirements drafting and contract management (where appropriate).</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -2282,43 +2282,43 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>worldbank_supply_chain_mgmt::c019</t>
+          <t>worldbank_supply_chain_mgmt::c005</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>cand_022</t>
+          <t>cand_018</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>What is the title of the book mentioned in the passage about supply chain management?</t>
+          <t>What is the Open Contracting Data Standard (OCDS)?</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>The title of the book mentioned in the passage is 'Supply-Chain-Management in stürmischen Zeiten'.</t>
+          <t>The Open Contracting Data Standard (OCDS) is a free, non-proprietary open data standard for public contracting, implemented by over 30 governments around the world. It describes how to publish data and documents about contracting processes for goods, works and services.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11 Collaboration 26 See also edit Supply chain security Cybersecurity Volume risk References edit cf. Andreas Wieland, Carl Marcus Wallenburg (2011): Supply-Chain-Management in stürmischen Zeiten . Berlin. Heckmann, Iris; Comes, Tina; Nickel, Stefan (2015). "A Critical Review on Supply Chain Risk – Definition, Measure and Modeling" Omega 52 (April 2015): 119– 132. doi 10.1108/09600031211281411 hdl 10398/9016 Brindley, Clare (2004). Supply Chain Risk . England: Ashgate Publishing Ltd. p. 80. ISBN 0-7546-3902-9 McKinsey, Understanding supply chain risk: A McKinsey Global Survey</t>
+          <t>Docs Primer What is the OCDS and why use it? View page source What is the OCDS and why use it? Â¶ Objectives This page will: Introduce the Open Contracting Data Standard (OCDS) Show the key concepts behind the OCDS Describe the relationship between the OCDS and open contracting The Open Contracting Data Standard (OCDS) is a free, non-proprietary open data standard for public contracting, implemented by over 30 governments around the world. It describes how to publish data and documents about contracting processes for goods, works and services. There are three concepts behind the Open Contracting Data Standard: Open Contracting is about publishing and using open, accessible and timely information on public contracting to engage citizens and businesses to fix problems and deliver results. These results include improving the efficiency, effectiveness and integrity of a public contracting system. Open Data is data that can be freely used, modified, and shared by anyone for any purpose. This requires data to be accessible and machine-readable, and for permission to be granted for reuse. Data Standard defines the structure and meaning of data in order to resolve ambiguity and help systems and people interpret it.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Supply_chain_risk_management</t>
+          <t>https://standard.open-contracting.org/latest/en/primer/what/</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>risk and sustainability</t>
+          <t>e-procurement and data standards</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.973</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1</v>
@@ -2347,58 +2347,58 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Supply-Chain-Management in stürmischen Zeiten . Berlin.</t>
+          <t>The Open Contracting Data Standard (OCDS) is a free, non-proprietary open data standard for public contracting, implemented by over 30 governments around the world. It describes how to publish data and documents about contracting processes for goods, works and services.</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>CC BY-SA 4.0</t>
+          <t>Apache-2.0 / CC-BY (Open Contracting Partnership)</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>wikipedia_supplier_risk</t>
+          <t>ocds_primer_what</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>wikipedia_supplier_risk::c014</t>
+          <t>ocds_primer_what::c000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>cand_023</t>
+          <t>cand_021</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>What are the responsibilities of the seller and buyer under an FOB contract according to Incoterms 1980?</t>
+          <t>What conditions must be met for a contract to be considered nonresponsible under the given criteria?</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Under an FOB contract, the seller is responsible for delivering the goods on board a vessel designated by the buyer, and arranging for export clearance. The buyer is responsible for the cost of marine freight transportation, bill of lading fees, insurance, unloading, and transportation costs from the arrival port to the destination. However, FOB should only be used for non-containerized seafreight and inland waterway transport, and its use for all modes of transport can introduce contractual risks.</t>
+          <t>A contract is considered nonresponsible if it is valued at more than the simplified acquisition threshold, the determination of nonresponsibility is based on a lack of satisfactory performance record or a satisfactory record of integrity and business ethics, and the Small Business Administration does not issue a Certificate of Competency.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21 Therefore, FOB contract requires a seller to deliver goods on board a vessel that is to be designated by the buyer in a manner customary at the particular port. In this case, the seller must also arrange for export clearance. On the other hand, the buyer pays cost of marine freight transportation, bill of lading fees, insurance, unloading and transportation cost from the arrival port to destination. Since Incoterms 1980 introduced the Incoterm FCA, FOB should only be used for non-containerized seafreight and inland waterway transport. However, FOB is commonly used incorrectly for all modes of transport despite the contractual risks that this can introduce. In some common law countries such as the United States of America</t>
+          <t>) if- (A) The contract is valued at more than the simplified acquisition threshold (B) The determination of nonresponsibility is based on lack of satisfactory performance record or satisfactory record of integrity and business ethics; and (C) The Small Business Administration does not issue a Certificate of Competency. (ii) The contracting officer is responsible for the timely submission, within 3 working days, and sufficiency, and accuracy of the documentation regarding the nonresponsibility determination. (iii) As required by section 3010 of the Supplemental Appropriations Act, 2010 (Pub. L. 111-212), all information posted in FAPIIS on or after April 15, 2011, except past performance reviews, will be publicly available.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Incoterms</t>
+          <t>https://www.acquisition.gov/far/part-9</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>logistics and KPIs</t>
+          <t>contract management</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.944</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1</v>
@@ -2427,58 +2427,58 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>FOB contract requires a seller to deliver goods on board a vessel that is to be designated by the buyer in a manner customary at the particular port. In this case, the seller must also arrange for export clearance. On the other hand, the buyer pays cost of marine freight transportation, bill of lading fees, insurance, unloading and transportation cost from the arrival port to destination. Since Incoterms 1980 introduced the Incoterm FCA, FOB should only be used for non-containerized seafreight and inland waterway transport. However, FOB is commonly used incorrectly for all modes of transport despite the contractual risks that this can introduce.</t>
+          <t>(A) The contract is valued at more than the simplified acquisition threshold (B) The determination of nonresponsibility is based on lack of satisfactory performance record or satisfactory record of integrity and business ethics; and (C) The Small Business Administration does not issue a Certificate of Competency.</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>CC BY-SA 4.0</t>
+          <t>US Government public domain</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>wikipedia_incoterms</t>
+          <t>far_part9_qualifications</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>wikipedia_incoterms::c019</t>
+          <t>far_part9_qualifications::c033</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>cand_025</t>
+          <t>cand_022</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>What is the ultimate goal of the OCDS according to the passage?</t>
+          <t>What is the purpose of reviewing supply chain risk in procurement?</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>The ultimate goal of the OCDS is to help deliver open contracting using standardized open data.</t>
+          <t>The purpose of reviewing supply chain risk in procurement is to identify and manage potential risks that could impact the supply chain, ensuring the stability and security of the supply chain.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>The OCDS builds on all three of these concepts, and the ultimate goal of the OCDS is to help deliver open contracting using standardized open data. The OCDS describes how to publish data and documents for the procurement of goods, works, and services. It makes contracting data available for anyone to use, modify, and share, for any purpose. The OCDS can be adapted to meet your needs. Whether purchasing medicines, running a municipal recycling program or building an airport, the OCDS helps you organize and publish all relevant data and documents during the process. The OCDS is not an electronic procurement system or database. But it can inform how data is collected, stored and published in these systems. The OCDS can help make sure that the contracting data you collect and publish meet global best practices and are fit-for-purpose to meet the needs of a range of different users. The OCDS helps to increase transparency, enables deeper analysis of contracting data, and facilitates the use of data by a wide range of stakeholders.</t>
+          <t>11 Collaboration 26 See also edit Supply chain security Cybersecurity Volume risk References edit cf. Andreas Wieland, Carl Marcus Wallenburg (2011): Supply-Chain-Management in stürmischen Zeiten . Berlin. Heckmann, Iris; Comes, Tina; Nickel, Stefan (2015). "A Critical Review on Supply Chain Risk – Definition, Measure and Modeling" Omega 52 (April 2015): 119– 132. doi 10.1108/09600031211281411 hdl 10398/9016 Brindley, Clare (2004). Supply Chain Risk . England: Ashgate Publishing Ltd. p. 80. ISBN 0-7546-3902-9 McKinsey, Understanding supply chain risk: A McKinsey Global Survey</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://standard.open-contracting.org/latest/en/primer/what/</t>
+          <t>https://en.wikipedia.org/wiki/Supply_chain_risk_management</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>e-procurement and data standards</t>
+          <t>risk and sustainability</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.93</v>
+        <v>0.916</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>1</v>
@@ -2497,54 +2497,54 @@
         <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>The OCDS builds on all three of these concepts, and the ultimate goal of the OCDS is to help deliver open contracting using standardized open data.</t>
+          <t>A Critical Review on Supply Chain Risk – Definition, Measure and Modeling</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Apache-2.0 / CC-BY (Open Contracting Partnership)</t>
+          <t>CC BY-SA 4.0</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>ocds_primer_what</t>
+          <t>wikipedia_supplier_risk</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>ocds_primer_what::c001</t>
+          <t>wikipedia_supplier_risk::c014</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>cand_026</t>
+          <t>cand_023</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>What is the name of the United Nations code used for trade and transport locations mentioned in the passage?</t>
+          <t>What does FOB stand for in procurement and supply chain contracts?</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>The United Nations Code for Trade and Transport Locations (UN/LOCODE) is mentioned in the passage.</t>
+          <t>FOB stands for Free On Board in procurement and supply chain contracts.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine United Nations Code for Trade and Transport Locations (UN/LOCODE) International trade Terminology Absolute advantage Balance of payments Balance of trade Capital account Comparative advantage Current account Export-oriented industrialization Fair trade Foreign exchange reserves Globalization Global labor arbitrage Import substitution industrialization Multinational corporation Net capital outflow Outsourcing Tariff Trade justice Trade war Trading nation Organizations and policies International Monetary Fund UN Trade and Development World Bank Group World Trade Organization International Trade Centre International Chamber of Commerce Bilateral investment treaty Economic integration Incoterms ATA Carnet Free-trade zone Special economic zone Trade agreement Trade barrier Trade bloc Political economy Free trade Adam Smith The Wealth of Nations Corn Laws Mercantilism Protectionism Economic nationalism Autarky Dedollarisation Withdrawal from the eurozone Regional organizations Americas Andean Community Caribbean Community Central American Integration System Mercosur Asia-Pacific Association of Southeast Asian Nations Regional Comprehensive Economic Partnership South Asian Association for Regional Cooperation Europe, Central Asia, and North Asia Customs Union of the Eurasian Economic Union Eurasian Economic Union European Union Customs Union Middle East and North Africa Arab Customs Union Gulf Cooperation Council Subsaharan Africa East African Community Economic and Monetary Community of Central Africa Southern African Customs Union West African Economic and Monetary Union Exports by product</t>
+          <t>21 Therefore, FOB contract requires a seller to deliver goods on board a vessel that is to be designated by the buyer in a manner customary at the particular port. In this case, the seller must also arrange for export clearance. On the other hand, the buyer pays cost of marine freight transportation, bill of lading fees, insurance, unloading and transportation cost from the arrival port to destination. Since Incoterms 1980 introduced the Incoterm FCA, FOB should only be used for non-containerized seafreight and inland waterway transport. However, FOB is commonly used incorrectly for all modes of transport despite the contractual risks that this can introduce. In some common law countries such as the United States of America</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -2554,11 +2554,11 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>procurement policy and compliance</t>
+          <t>logistics and KPIs</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.836</v>
+        <v>0.878</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>1</v>
@@ -2577,17 +2577,17 @@
         <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>5</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine United Nations Code for Trade and Transport Locations (UN/LOCODE) International trade</t>
+          <t>21 Therefore, FOB contract requires a seller to deliver goods on board a vessel that is to be designated by the buyer in a manner customary at the particular port.</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2602,43 +2602,43 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>wikipedia_incoterms::c040</t>
+          <t>wikipedia_incoterms::c019</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>cand_027</t>
+          <t>cand_025</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>What are the two types of financing provided by the Bank under Investment Project Financing (IPF)?</t>
+          <t>What is the purpose of the OCDS?</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>The two types of financing provided by the Bank under Investment Project Financing (IPF) are an IBRD loan or an IDA credit/grant or guarantee.</t>
+          <t>The OCDS helps to increase transparency, enables deeper analysis of contracting data, and facilitates the use of data by a wide range of stakeholders.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>FIGURE 1 The five World Bank Group Institutions SECTION I: INTRODUCTION Investment Project Financing Investment Project Financing (IPF) is one of the ways in which Bank financing is provided to countries. This financing may take the form of an IBRD loan or IDA credit/grant or guarantee. IPF supports projects with defined development objectives, activities, and results, and disburses the financing against specific eligible expenditures. IPF provides funding for activities that produce the physical/ social infrastructure necessary to reduce poverty and create sustainable development. To create this</t>
+          <t>The OCDS builds on all three of these concepts, and the ultimate goal of the OCDS is to help deliver open contracting using standardized open data. The OCDS describes how to publish data and documents for the procurement of goods, works, and services. It makes contracting data available for anyone to use, modify, and share, for any purpose. The OCDS can be adapted to meet your needs. Whether purchasing medicines, running a municipal recycling program or building an airport, the OCDS helps you organize and publish all relevant data and documents during the process. The OCDS is not an electronic procurement system or database. But it can inform how data is collected, stored and published in these systems. The OCDS can help make sure that the contracting data you collect and publish meet global best practices and are fit-for-purpose to meet the needs of a range of different users. The OCDS helps to increase transparency, enables deeper analysis of contracting data, and facilitates the use of data by a wide range of stakeholders.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://thedocs.worldbank.org/en/doc/caf6a3f677305292d799dbe55fd83bfe-0290012023/original/PROCUREMENT-Beginners-Guide-to-IPF-WEB-VERSION-Nov-2023.pdf</t>
+          <t>https://standard.open-contracting.org/latest/en/primer/what/</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>tender process</t>
+          <t>e-procurement and data standards</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.949</v>
+        <v>0.948</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>1</v>
@@ -2657,68 +2657,68 @@
         <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>This financing may take the form of an IBRD loan or IDA credit/grant or guarantee.</t>
+          <t>The OCDS helps to increase transparency, enables deeper analysis of contracting data, and facilitates the use of data by a wide range of stakeholders.</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>CC BY 3.0 IGO (World Bank open access)</t>
+          <t>Apache-2.0 / CC-BY (Open Contracting Partnership)</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>worldbank_beginners_guide</t>
+          <t>ocds_primer_what</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>worldbank_beginners_guide::c017</t>
+          <t>ocds_primer_what::c001</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>cand_031</t>
+          <t>cand_026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Under what circumstances would an independent contractor not be considered a marketing consultant according to the passage?</t>
+          <t>What is the purpose of a trade agreement?</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>An independent contractor would not be considered a marketing consultant if they provide services that are excluded in subpart 37.2, such as routine engineering and technical services, routine legal, actuarial, auditing, and accounting services, and training services.</t>
+          <t>The purpose of a trade agreement is to facilitate international trade by reducing trade barriers and establishing rules for trade between countries.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>An independent contractor is not a marketing consultant when rendering- (1) Services excluded in subpart  37.2 (2) Routine engineering and technical services (such as installation, operation, or maintenance of systems, equipment, software, components , or facilities); (3) Routine legal, actuarial, auditing, and accounting services; and (4) Training services. 9.502 Applicability. (a) This subpart applies to contracts with either profit or nonprofit organizations, including nonprofit organizations created largely or wholly with Government funds.</t>
+          <t>Wayback Machine United Nations Code for Trade and Transport Locations (UN/LOCODE) International trade Terminology Absolute advantage Balance of payments Balance of trade Capital account Comparative advantage Current account Export-oriented industrialization Fair trade Foreign exchange reserves Globalization Global labor arbitrage Import substitution industrialization Multinational corporation Net capital outflow Outsourcing Tariff Trade justice Trade war Trading nation Organizations and policies International Monetary Fund UN Trade and Development World Bank Group World Trade Organization International Trade Centre International Chamber of Commerce Bilateral investment treaty Economic integration Incoterms ATA Carnet Free-trade zone Special economic zone Trade agreement Trade barrier Trade bloc Political economy Free trade Adam Smith The Wealth of Nations Corn Laws Mercantilism Protectionism Economic nationalism Autarky Dedollarisation Withdrawal from the eurozone Regional organizations Americas Andean Community Caribbean Community Central American Integration System Mercosur Asia-Pacific Association of Southeast Asian Nations Regional Comprehensive Economic Partnership South Asian Association for Regional Cooperation Europe, Central Asia, and North Asia Customs Union of the Eurasian Economic Union Eurasian Economic Union European Union Customs Union Middle East and North Africa Arab Customs Union Gulf Cooperation Council Subsaharan Africa East African Community Economic and Monetary Community of Central Africa Southern African Customs Union West African Economic and Monetary Union Exports by product</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.acquisition.gov/far/part-9</t>
+          <t>https://en.wikipedia.org/wiki/Incoterms</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>supplier evaluation</t>
+          <t>procurement policy and compliance</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.962</v>
+        <v>0.823</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>1</v>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -2747,58 +2747,58 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>An independent contractor is not a marketing consultant when rendering- (1) Services excluded in subpart 37.2 (2) Routine engineering and technical services (such as installation, operation, or maintenance of systems, equipment, software, components , or facilities); (3) Routine legal, actuarial, auditing, and accounting services; and (4) Training services.</t>
+          <t>Trade agreement Trade barrier Trade bloc</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>US Government public domain</t>
+          <t>CC BY-SA 4.0</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>far_part9_qualifications</t>
+          <t>wikipedia_incoterms</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>far_part9_qualifications::c180</t>
+          <t>wikipedia_incoterms::c040</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>cand_032</t>
+          <t>cand_031</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>What journal published the article 'Surging Energy Prices in Europe in the Aftermath of the War: How to Support the Vulnerable and Speed up the Transition Away from Fossil Fuels'?</t>
+          <t>Under what circumstances is an independent contractor not considered a marketing consultant?</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Journal of Cleaner Production</t>
+          <t>An independent contractor is not considered a marketing consultant when rendering services that are excluded in subpart 37.2, routine engineering and technical services (such as installation, operation, or maintenance of systems, equipment, software, components, or facilities), routine legal, actuarial, auditing, and accounting services, and training services.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Review Between 1996 and 2013. Journal of Cleaner Production, 85. Ari, A., Arregui, N., Black, S., Celasun, O., Iakova, D., et al. (2022). Surging Energy Prices in Europe in the Aftermath of the War: How to Support the Vulnerable and Speed up the Transition Away from Fossil Fuels. Barrad, S., Gagnon, S., and Valverde, R. (2020). An An- alytics Architecture for Procurement. International Journal of Information Technologies and Systems Ap-</t>
+          <t>An independent contractor is not a marketing consultant when rendering- (1) Services excluded in subpart  37.2 (2) Routine engineering and technical services (such as installation, operation, or maintenance of systems, equipment, software, components , or facilities); (3) Routine legal, actuarial, auditing, and accounting services; and (4) Training services. 9.502 Applicability. (a) This subpart applies to contracts with either profit or nonprofit organizations, including nonprofit organizations created largely or wholly with Government funds.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://arxiv.org/pdf/2303.03882</t>
+          <t>https://www.acquisition.gov/far/part-9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>e-procurement and data standards</t>
+          <t>supplier evaluation</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.87</v>
+        <v>0.981</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>1</v>
@@ -2827,58 +2827,58 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Review Between 1996 and 2013. Journal of Cleaner Production, 85. Ari, A., Arregui, N., Black, S., Celasun, O., Iakova, D., et al. (2022). Surging Energy Prices in Europe in the Aftermath of the War: How to Support the Vulnerable and Speed up the Transition Away from Fossil Fuels.</t>
+          <t>An independent contractor is not a marketing consultant when rendering- (1) Services excluded in subpart  37.2 (2) Routine engineering and technical services (such as installation, operation, or maintenance of systems, equipment, software, components , or facilities); (3) Routine legal, actuarial, auditing, and accounting services; and (4) Training services.</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>arXiv.org perpetual non-exclusive license (open access)</t>
+          <t>US Government public domain</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>arxiv_digital_procurement</t>
+          <t>far_part9_qualifications</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>arxiv_digital_procurement::c064</t>
+          <t>far_part9_qualifications::c180</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>cand_033</t>
+          <t>cand_037</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>What are the Borrower's responsibilities in carrying out procurement activities financed by the Bank?</t>
+          <t>What does CFR stand for in international trade?</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>The Borrower is responsible for planning the procurement, preparing a procurement strategy, inviting offers from the market, evaluating offers and determining the Most Advantageous Bid/Proposal, and awarding, signing, and managing contracts. These responsibilities are outlined in the passage as part of the Borrower's role in procurement activities financed by the Bank.</t>
+          <t>CFR stands for Cost and Freight.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>However, several aspects of the Guidance are also relevant for projects subject to the Guidelines. Roles and Responsibilities Borrower The Borrower is responsible for carrying out procurement activities financed by the Bank in accordance with the financing agreement signed between the Bank and the Borrower. In particular, the Borrower must use funds only for the purpose for which they were granted. Other responsibilities include: 1. planning the procurement 2. preparing a procurement strategy for the project, as defined in the Project Procurement Strategy for Development (PPSD) 3. inviting offers from the market 4. evaluating offers and determining the Most Advantageous Bid/Proposal (MABP) 5. awarding, signing, and managing contracts. Bank To ensure that funds are used only for the purpose for which they were granted, the Bank provides Borrowers with procurement implementation support and oversight for each project. Implementation support includes providing training and advice to the Borrower. The Bank conducts its procurement oversight function in order to discharge its fiduciary responsibilities, as required by the Bank’s Articles of Agreement. Prior and Post Reviews This fiduciary responsibility entails the Bank conducting reviews of selected procurement activities</t>
+          <t>, FOB is not only connected with the carriage of goods by sea but also used for inland carriage aboard any "vessel, car or other vehicle." 22 CFR – Cost and Freight (named port of destination) edit The seller pays for the carriage of the goods up to the named port of destination. Risk transfers to buyer when the goods have been loaded on board the ship in the country of Export. The seller is responsible for origin costs including export clearance and freight costs for carriage to the named port. The shipper is not responsible for delivery to the final destination from the port (generally the buyer's facilities), or for buying insurance. If the buyer requires the seller to obtain insurance, the Incoterm CIF should be considered. CFR should only be used for non-containerized seafreight and inland waterway transport; for all other modes of transport it should be replaced with CPT. CIF – Cost, Insurance &amp; Freight (named port of destination) edit Use preceding Incoterms edit</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://thedocs.worldbank.org/en/doc/caf6a3f677305292d799dbe55fd83bfe-0290012023/original/PROCUREMENT-Beginners-Guide-to-IPF-WEB-VERSION-Nov-2023.pdf</t>
+          <t>https://en.wikipedia.org/wiki/Incoterms</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>procurement policy and compliance</t>
+          <t>logistics and KPIs</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.864</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>1</v>
@@ -2890,75 +2890,75 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>5</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Other responsibilities include: 1. planning the procurement 2. preparing a procurement strategy for the project, as defined in the Project Procurement Strategy for Development (PPSD) 3. inviting offers from the market 4. evaluating offers and determining the Most Advantageous Bid/Proposal (MABP) 5. awarding, signing, and managing contracts.</t>
+          <t>22 CFR – Cost and Freight (named port of destination) edit The seller pays for the carriage of the goods up to the named port of destination.</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>CC BY 3.0 IGO (World Bank open access)</t>
+          <t>CC BY-SA 4.0</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>worldbank_beginners_guide</t>
+          <t>wikipedia_incoterms</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>worldbank_beginners_guide::c027</t>
+          <t>wikipedia_incoterms::c020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>cand_034</t>
+          <t>cand_038</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>What are the two main institutions that make up the World Bank?</t>
+          <t>What is the purpose of early consideration of additional sustainable procurement requirements in the procurement process?</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The two main institutions that make up the World Bank are the International Bank for Reconstruction and Development (IBRD) and the International Development Association (IDA).</t>
+          <t>Early consideration of additional sustainable procurement requirements ensures that they are included in the overall procurement approach, which may be designed to consider such requirements at a number of stages of the procurement process, such as prequalification or initial selection of bidders, functional or detailed technical specifications, evaluation criteria, including the use of rated criteria, contract terms and conditions, and contract performance monitoring.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>World Bank The World Bank comprises two WBG institutions, the International Bank for Reconstruction and Development (IBRD), which assists middle-income and creditworthy poorer countries, and the International Development Association (IDA), which focuses on the world’s poorest countries. World Bank Group (WBG) The World Bank Group is a unique global partnership of five institutions working for sustainable solutions that reduce poverty and build shared prosperity in developing countries. The five institutions are the IBRD, IDA, IFC, MIGA, and ICSID. Contents Common Abbreviations and Defined Terms  . . . . . . . . . . . . . . . . . . . . . . . . . . i SECTION I . Introduction  . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 1 Purpose ......................................................................... 1 World Bank Group ................................................................ 1 World Bank ................................................................... 2 Investment Project Financing ....................................................... 3</t>
+          <t>apply additional sustainable Procurement requirements and the manner in which they will be handled in evaluation, such as in the application of Rated Criteria, should be detailed in the PPSD. Early Identification Early consideration of additional sustainable Procurement requirements ensures that they are included in the overall Procurement Approach, which may be designed to consider such requirements at a number of stages of the Procurement Process, such as ◾ Prequalification or Initial Selection of Bidders ◾ Functional or detailed technical specifications ◾ Evaluation Criteria, including the use of Rated Criteria ◾ Contract terms and conditions ◾ Contract performance monitoring.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://thedocs.worldbank.org/en/doc/caf6a3f677305292d799dbe55fd83bfe-0290012023/original/PROCUREMENT-Beginners-Guide-to-IPF-WEB-VERSION-Nov-2023.pdf</t>
+          <t>https://thedocs.worldbank.org/en/doc/a535313d21a71139c93f09311e274093-0290012023/original/Procurement-Guidance-Value-for-Money-Nov-2023-WEB.pdf</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>tender process</t>
+          <t>supplier evaluation</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.618</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>1</v>
@@ -2970,11 +2970,11 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1</v>
+        <v>0.498</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>5</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>World Bank comprises two WBG institutions, the International Bank for Reconstruction and Development (IBRD), which assists middle-income and creditworthy poorer countries, and the International Development Association (IDA), which focuses on the world’s poorest countries.</t>
+          <t>Early consideration of additional sustainable Procurement requirements ensures that they are included in the overall Procurement Approach, which may be designed to consider such requirements at a number of stages of the Procurement Process, such as Prequalification or Initial Selection of Bidders, Functional or detailed technical specifications, Evaluation Criteria, including the use of Rated Criteria, Contract terms and conditions, Contract performance monitoring.</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2997,34 +2997,34 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>worldbank_beginners_guide</t>
+          <t>worldbank_value_for_money</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>worldbank_beginners_guide::c007</t>
+          <t>worldbank_value_for_money::c042</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>cand_035</t>
+          <t>cand_041</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>What must a request for waiver include according to the passage?</t>
+          <t>Under what condition should a contractor not be awarded a contract for evaluating offers in procurement?</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>A request for waiver must be in writing, set forth the extent of the conflict, and require approval by the agency head or a designee.</t>
+          <t>A contractor should not be awarded a contract for evaluating its own offers or those of a competitor without proper safeguards to ensure objectivity and protect the Government’s interests.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9.503 Waiver. The agency head or a designee may waive any general rule or procedure of this subpart by determining that its application in a particular situation would not be in the Government’s interest. Any request for waiver must be in writing shall set forth the extent of the conflict, and requires approval by the agency head or a designee. Agency heads shall not delegate waiver authority below the level of head of a contracting activity 9.504 Contracting officer responsibilities. (a) Using the general rules, procedures, and examples in this subpart, contracting officers shall analyze planned acquisitions in order to- (1) Identify and evaluate potential organizational conflicts of interest as early in the acquisition process as possible; and (2) Avoid, neutralize, or mitigate significant potential conflicts before contract award. (b) Contracting officers should obtain the advice of counsel and the assistance of appropriate technical specialists in evaluating potential conflicts and in developing any necessary solicitation provisions and contract clauses (see 9.506 ). (c) Before issuing a solicitation for a contract that may involve a significant potential conflict, the contracting officer shall recommend to the head of the contracting activity</t>
+          <t>9.505-3 Providing evaluation services. Contracts for the evaluation of offers for products or services shall not be awarded to a contractor that will evaluate its own offers for products or services, or those of a competitor, without proper safeguards to ensure objectivity to protect the Government’s interests. 9.505-4 Obtaining access to proprietary information. (a) When a contractor requires proprietary information from others to perform a Government contract and can use the leverage of the contract to obtain it, the contractor</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -3034,11 +3034,11 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>contract management</t>
+          <t>tender process</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.887</v>
+        <v>0.905</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>1</v>
@@ -3057,17 +3057,17 @@
         <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>5</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Any request for waiver must be in writing shall set forth the extent of the conflict, and requires approval by the agency head or a designee.</t>
+          <t>Contracts for the evaluation of offers for products or services shall not be awarded to a contractor that will evaluate its own offers for products or services, or those of a competitor, without proper safeguards to ensure objectivity to protect the Government’s interests.</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>far_part9_qualifications::c183</t>
+          <t>far_part9_qualifications::c195</t>
         </is>
       </c>
     </row>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>What should be included in the contract management plan if KPIs are linked to incentive mechanisms or payment decisions?</t>
+          <t>What should KPIs be included in to ensure alignment with the desired outcome in contract management?</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>If KPIs are linked to incentive mechanisms or payment decisions, they will need to be agreed to and included as part of the contract before it is signed.</t>
+          <t>KPIs should be included in the contract management plan.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.948</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>1</v>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>if they link to incentive mechanisms or payment decisions, they will need to be agreed to and included as part of the contract before it is signed.</t>
+          <t>The KPIs should be included in the contract management plan,</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>What does viability in supply chains focus on beyond just structural stability and recoverability?</t>
+          <t>What does the term 'viability' refer to in the context of supply chains?</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Viability in supply chains focuses on the ongoing survival and service provision under both acute disruptions and long-term, evolving pressures by integrating resilience with sustainability and adaptive reconfiguration.</t>
+          <t>Viability refers to a supply chain's capability of ongoing survival and service provision under both acute disruptions and long-term, evolving pressures by integrating resilience with sustainability and adaptive reconfiguration.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3198,36 +3198,36 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.945</v>
+        <v>0.926</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>analytical</t>
+          <t>factual</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>5</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>viability frames a supply chain not just as recoverable or structurally stable, but as capable of ongoing survival and service provision under both acute disruptions and long-term, evolving pressures by integrating resilience with sustainability and adaptive reconfiguration.</t>
+          <t>Extending these, viability frames a supply chain not just as recoverable or structurally stable, but as capable of ongoing survival and service provision under both acute disruptions and long-term, evolving pressures by integrating resilience with sustainability and adaptive reconfiguration.</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3249,43 +3249,43 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>cand_045</t>
+          <t>cand_044</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>What are some ways to optimize value for money (VfM) in the procurement process according to the passage?</t>
+          <t>What is the difference between the FAS and FOB terms regarding export clearance responsibilities?</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>To optimize value for money (VfM) in the procurement process, the following steps can be taken: ensuring integrity throughout the process, identifying and factoring the needs of end users and other stakeholders, mitigating risks through the design of procurement arrangements, ensuring that procurement arrangements are fit for purpose, providing opportunities for cost-effective and innovative solutions, and basing contract award decisions on suitable evaluation criteria. These steps help to effectively, efficiently, and economically use the resources available to a project.</t>
+          <t>The FAS term requires the seller to clear the goods for export, which is a reversal from previous Incoterms versions that required the buyer to arrange for export clearance. However, if the parties wish the buyer to clear the goods for export, this should be made clear by adding explicit wording to this effect in the contract of sale.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Optimizing VfM The Procurement Process includes numerous opportunities to address VfM. This supports develop- ing a fit-for-purpose Procurement Approach that is both country and project specific. Figure I demonstrates that VfM elements can be individual and cumulative and exist throughout the Procurement Process to more effectively, efficiently, and economically use the resources available to a project, in other words, to optimize VfM. Examples include ensuring: ◾ Integrity throughout the Procurement Process ◾ That the needs of end users and other stakeholders are appropriately identified and factored into the Procurement Arrangements ◾ That risks to achieving the required objectives are appropriately identified and mitigated through design of the Procurement Arrangements ◾ That the Procurement Arrangements are fit for purpose relative to the risk, value, and complex- ity of the Procurement and to the operating context and nature of the supply market ◾ When appropriate, that providers are given the opportunity to offer cost-effective and innova- tive solutions to meet identified needs ◾ That contract award decisions are based on suitable Evaluation Criteria and when appropriate the use of Rated Criteria</t>
+          <t>The FAS term requires the seller to clear the goods for export, which is a reversal from previous Incoterms versions that required the buyer to arrange for export clearance. However, if the parties wish the buyer to clear the goods for export, this should be made clear by adding explicit wording to this effect in the contract of sale. This term should be used only for non-containerized sea freight and inland waterway transport. FOB – Free on Board (named port of shipment) edit Main article: FOB (Shipping) Under FOB terms the seller bears all costs and risks up to the point the goods are loaded on board the vessel. The seller's responsibility does not end at that point unless the goods are "appropriated to the contract" that is, they are "clearly set aside or otherwise identified as the contract goods".</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://thedocs.worldbank.org/en/doc/a535313d21a71139c93f09311e274093-0290012023/original/Procurement-Guidance-Value-for-Money-Nov-2023-WEB.pdf</t>
+          <t>https://en.wikipedia.org/wiki/Incoterms</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>supplier evaluation</t>
+          <t>logistics and KPIs</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>analytical</t>
+          <t>factual</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -3294,57 +3294,57 @@
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.778</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>5</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Examples include ensuring: ◾ Integrity throughout the Procurement Process ◾ That the needs of end users and other stakeholders are appropriately identified and factored into the Procurement Arrangements ◾ That risks to achieving the required objectives are appropriately identified and mitigated through design of the Procurement Arrangements ◾ That the Procurement Arrangements are fit for purpose relative to the risk, value, and complexity of the Procurement and to the operating context and nature of the supply market ◾ When appropriate, that providers are given the opportunity to offer cost-effective and innovative solutions to meet identified needs ◾ That contract award decisions are based on suitable Evaluation Criteria and when appropriate the use of Rated Criteria</t>
+          <t>The FAS term requires the seller to clear the goods for export, which is a reversal from previous Incoterms versions that required the buyer to arrange for export clearance. However, if the parties wish the buyer to clear the goods for export, this should be made clear by adding explicit wording to this effect in the contract of sale.</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>CC BY 3.0 IGO (World Bank open access)</t>
+          <t>CC BY-SA 4.0</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>worldbank_value_for_money</t>
+          <t>wikipedia_incoterms</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>worldbank_value_for_money::c017</t>
+          <t>wikipedia_incoterms::c018</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>cand_048</t>
+          <t>cand_045</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>What factors influence the choice of selection method for each contract?</t>
+          <t>What is the purpose of addressing VfM elements in the procurement process?</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>The choice of selection method for each contract is influenced by the capacity and level of competition in the market, the number of qualified bidders available, the specificity, complexity, and nature of the procurement requirement, and the inherent risks involved in the contract, as well as how these risks may best be mitigated through the procurement process and resulting contract.</t>
+          <t>The purpose of addressing VfM elements in the procurement process is to more effectively, efficiently, and economically use the resources available to a project, in other words, to optimize VfM.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Bid or Proposal for each contract. The choice of selection method to be used for each contract is driven by a number of factors: ◾ Primarily by the capacity and level of competition in the market ◾ Number of qualified Bidders available ◾ Specificity, complexity, and nature of the Procurement requirement ◾ Inherent risks involved in the contract, as well as how the identified risks may best be mitigated through the Procurement Process and resulting contract. Each combination of options will present a different trade-off between costs and benefits. VALUE FOR MONEY: ACHIEVING VfM IN INVESTMENT PROJECTS FINANCED BY THE WORLD BANK</t>
+          <t>Optimizing VfM The Procurement Process includes numerous opportunities to address VfM. This supports develop- ing a fit-for-purpose Procurement Approach that is both country and project specific. Figure I demonstrates that VfM elements can be individual and cumulative and exist throughout the Procurement Process to more effectively, efficiently, and economically use the resources available to a project, in other words, to optimize VfM. Examples include ensuring: ◾ Integrity throughout the Procurement Process ◾ That the needs of end users and other stakeholders are appropriately identified and factored into the Procurement Arrangements ◾ That risks to achieving the required objectives are appropriately identified and mitigated through design of the Procurement Arrangements ◾ That the Procurement Arrangements are fit for purpose relative to the risk, value, and complex- ity of the Procurement and to the operating context and nature of the supply market ◾ When appropriate, that providers are given the opportunity to offer cost-effective and innova- tive solutions to meet identified needs ◾ That contract award decisions are based on suitable Evaluation Criteria and when appropriate the use of Rated Criteria</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3354,11 +3354,11 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>tender process</t>
+          <t>supplier evaluation</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.766</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>1</v>
@@ -3370,11 +3370,11 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1</v>
+        <v>0.778</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>5</v>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>The choice of selection method to be used for each contract is driven by a number of factors: ◾ Primarily by the capacity and level of competition in the market ◾ Number of qualified Bidders available ◾ Specificity, complexity, and nature of the Procurement requirement ◾ Inherent risks involved in the contract, as well as how the identified risks may best be mitigated through the Procurement Process and resulting contract.</t>
+          <t>Examples include ensuring: ◾ Integrity throughout the Procurement Process ◾ That the needs of end users and other stakeholders are appropriately identified and factored into the Procurement Arrangements ◾ That risks to achieving the required objectives are appropriately identified and mitigated through design of the Procurement Arrangements ◾ That the Procurement Arrangements are fit for purpose relative to the risk, value, and complexity of the Procurement and to the operating context and nature of the supply market ◾ When appropriate, that providers are given the opportunity to offer cost-effective and innovative solutions to meet identified needs ◾ That contract award decisions are based on suitable Evaluation Criteria and when appropriate the use of Rated Criteria</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3402,43 +3402,43 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>worldbank_value_for_money::c033</t>
+          <t>worldbank_value_for_money::c017</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>cand_049</t>
+          <t>cand_048</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>What is WSLA and what does it allow authors to specify?</t>
+          <t>What factors influence the choice of selection method for a contract in procurement?</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>WSLA is a standard for service level agreement compliance monitoring of web services. It allows authors to specify the performance metrics associated with a web service application, desired performance targets, and actions that should be performed when performance is not met.</t>
+          <t>The choice of selection method for a contract is influenced by several factors, including the capacity and level of competition in the market, the number of qualified bidders available, the specificity, complexity, and nature of the procurement requirement, and the inherent risks involved in the contract, as well as how these risks may be mitigated through the procurement process and resulting contract.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10 Fixed networks edit For fixed networks subscribers, service modeling appears to be one of the most suitable ways to effectively monitor SLA's and ensure they are met. 11 WSLA edit web service level agreement WSLA ) is a standard for service level agreement compliance monitoring of web services . It allows authors to specify the performance metrics associated with a web service application, desired performance targets, and actions that should be performed when performance is not met. WSLA Language Specification, version 1.0 12 was published by IBM in 2001. Cloud computing edit The underlying benefit of cloud computing is shared resources, which are supported by the underlying nature of a shared infrastructure environment. Thus, SLAs span across the cloud and are offered by service providers as a service-based agreements rather than a customer-based agreements. Measuring, monitoring and reporting on cloud performance is based on the end UX or their ability to consume resources. The downside of cloud computing relative to SLAs is the difficulty in determining the root cause of service interruptions due to the complex nature of the environment.</t>
+          <t>Bid or Proposal for each contract. The choice of selection method to be used for each contract is driven by a number of factors: ◾ Primarily by the capacity and level of competition in the market ◾ Number of qualified Bidders available ◾ Specificity, complexity, and nature of the Procurement requirement ◾ Inherent risks involved in the contract, as well as how the identified risks may best be mitigated through the Procurement Process and resulting contract. Each combination of options will present a different trade-off between costs and benefits. VALUE FOR MONEY: ACHIEVING VfM IN INVESTMENT PROJECTS FINANCED BY THE WORLD BANK</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Service-level_agreement</t>
+          <t>https://thedocs.worldbank.org/en/doc/a535313d21a71139c93f09311e274093-0290012023/original/Procurement-Guidance-Value-for-Money-Nov-2023-WEB.pdf</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>contract management</t>
+          <t>tender process</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.926</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>1</v>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
@@ -3467,58 +3467,58 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>WSLA edit web service level agreement WSLA ) is a standard for service level agreement compliance monitoring of web services . It allows authors to specify the performance metrics associated with a web service application, desired performance targets, and actions that should be performed when performance is not met.</t>
+          <t>The choice of selection method to be used for each contract is driven by a number of factors: ◾ Primarily by the capacity and level of competition in the market ◾ Number of qualified Bidders available ◾ Specificity, complexity, and nature of the Procurement requirement ◾ Inherent risks involved in the contract, as well as how the identified risks may best be mitigated through the Procurement Process and resulting contract.</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>CC BY-SA 4.0</t>
+          <t>CC BY 3.0 IGO (World Bank open access)</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>wikipedia_sla</t>
+          <t>worldbank_value_for_money</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>wikipedia_sla::c006</t>
+          <t>worldbank_value_for_money::c033</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>cand_050</t>
+          <t>cand_049</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>What was the main objective of the sustainable public procurement project in France?</t>
+          <t>What is the purpose of a web service level agreement (WSLA)?</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>The main objective of the sustainable public procurement project in France was toner cartridges for laser printers.</t>
+          <t>A web service level agreement (WSLA) is a standard for service level agreement compliance monitoring of web services. It allows authors to specify the performance metrics associated with a web service application, desired performance targets, and actions that should be performed when performance is not met.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>21 Case studies edit The Marrakech Task Force on Sustainable Public Procurement (MTF or SPP) which was managed by Switzerland from 2006 to May 2011 established an approach for the effective implementation of sustainable procurement. This approach was named the MTF Approach to SPP. Since then, the United Nations Environmental Programme have worked together with the Swiss government to develop a project to implement sustainable procurement worldwide. The project named Capacity Building for Sustainable Public Procurement in Developing Countries was piloted in seven countries: Chile, Colombia, Costa Rica, Lebanon, Mauritius, Tunisia, and Uruguay. Since then, the list of countries adopting this newly designed approach to developing has increased, adding more advanced and industrialized nations to be used as case studies to measure the efficiency and benefits of the implementation of sustainable public procurement. In Brazil, the project involved recycled paper; in Costa Rica, the management services was redesigned; toner cartridges for laser printers were the main objective in France; in Hong Kong and China the nations aimed to improve traffic with LED traffic light retrofitting; organic food for school children was the focus in Italy; sustainable construction was the focus in England; consultancy and temporary staff services were renovated in Scotland; and in the United States, there was a push for the sustainable transportation of waste.</t>
+          <t>10 Fixed networks edit For fixed networks subscribers, service modeling appears to be one of the most suitable ways to effectively monitor SLA's and ensure they are met. 11 WSLA edit web service level agreement WSLA ) is a standard for service level agreement compliance monitoring of web services . It allows authors to specify the performance metrics associated with a web service application, desired performance targets, and actions that should be performed when performance is not met. WSLA Language Specification, version 1.0 12 was published by IBM in 2001. Cloud computing edit The underlying benefit of cloud computing is shared resources, which are supported by the underlying nature of a shared infrastructure environment. Thus, SLAs span across the cloud and are offered by service providers as a service-based agreements rather than a customer-based agreements. Measuring, monitoring and reporting on cloud performance is based on the end UX or their ability to consume resources. The downside of cloud computing relative to SLAs is the difficulty in determining the root cause of service interruptions due to the complex nature of the environment.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sustainable_procurement</t>
+          <t>https://en.wikipedia.org/wiki/Service-level_agreement</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>risk and sustainability</t>
+          <t>contract management</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.887</v>
+        <v>0.929</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>1</v>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>toner cartridges for laser printers were the main objective in France;</t>
+          <t>WSLA ) is a standard for service level agreement compliance monitoring of web services . It allows authors to specify the performance metrics associated with a web service application, desired performance targets, and actions that should be performed when performance is not met.</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,12 +3557,12 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>wikipedia_green_proc</t>
+          <t>wikipedia_sla</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>wikipedia_green_proc::c015</t>
+          <t>wikipedia_sla::c006</t>
         </is>
       </c>
     </row>
